--- a/resultado_teste/Midas_Lab_Backtest.xlsx
+++ b/resultado_teste/Midas_Lab_Backtest.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q205"/>
+  <dimension ref="A1:Q202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -461,7 +461,7 @@
     <col width="23" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
     <col width="17" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="17"/>
@@ -5887,7 +5887,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>ITSA3</t>
+          <t>LOGN3</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -5896,19 +5896,19 @@
         </is>
       </c>
       <c r="C84" s="3" t="n">
-        <v>41.9</v>
+        <v>38.7</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>14.17</v>
+        <v>32.25</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>13.09</v>
+        <v>29.75</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>-7.63</v>
+        <v>-7.75</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>14.89</v>
+        <v>13.62</v>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
@@ -5931,13 +5931,13 @@
         </is>
       </c>
       <c r="L84" s="3" t="n">
-        <v>1.02</v>
+        <v>6.68</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>7.66</v>
+        <v>21.44</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>-4.8511</v>
+        <v>-73.85769999999999</v>
       </c>
       <c r="O84" s="3" t="n">
         <v>0</v>
@@ -5952,32 +5952,32 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>LOGN3</t>
+          <t>SMFT3</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Não Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="C85" s="3" t="n">
-        <v>38.7</v>
+        <v>58.1</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>32.25</v>
+        <v>20.13</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>29.75</v>
+        <v>18.53</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>-7.75</v>
+        <v>-7.95</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>13.62</v>
+        <v>-1.76</v>
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="K85" s="3" t="inlineStr">
@@ -5996,13 +5996,13 @@
         </is>
       </c>
       <c r="L85" s="3" t="n">
-        <v>6.68</v>
+        <v>3.75</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>21.44</v>
+        <v>20.17</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>-73.85769999999999</v>
+        <v>-27.6763</v>
       </c>
       <c r="O85" s="3" t="n">
         <v>0</v>
@@ -6017,32 +6017,32 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>SMFT3</t>
+          <t>ALUP11</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Não Previsível</t>
         </is>
       </c>
       <c r="C86" s="3" t="n">
-        <v>58.1</v>
+        <v>46.8</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>20.13</v>
+        <v>35.44</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>18.53</v>
+        <v>32.57</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>-7.95</v>
+        <v>-8.1</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>-1.76</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="I86" s="3" t="inlineStr">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
@@ -6061,13 +6061,13 @@
         </is>
       </c>
       <c r="L86" s="3" t="n">
-        <v>3.75</v>
+        <v>2.07</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>20.17</v>
+        <v>6.19</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>-27.6763</v>
+        <v>-4.0247</v>
       </c>
       <c r="O86" s="3" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>ALUP11</t>
+          <t>TAEE11</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -6094,16 +6094,16 @@
         <v>46.8</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>35.44</v>
+        <v>42.65</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>32.57</v>
+        <v>39.16</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>-8.1</v>
+        <v>-8.19</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>8.029999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
@@ -6126,13 +6126,13 @@
         </is>
       </c>
       <c r="L87" s="3" t="n">
-        <v>2.07</v>
+        <v>5.2</v>
       </c>
       <c r="M87" s="3" t="n">
-        <v>6.19</v>
+        <v>12.92</v>
       </c>
       <c r="N87" s="3" t="n">
-        <v>-4.0247</v>
+        <v>-12.74</v>
       </c>
       <c r="O87" s="3" t="n">
         <v>0</v>
@@ -6147,7 +6147,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>TAEE11</t>
+          <t>CGAS5</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -6156,19 +6156,19 @@
         </is>
       </c>
       <c r="C88" s="3" t="n">
-        <v>46.8</v>
+        <v>33.9</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>42.65</v>
+        <v>135.3</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>39.16</v>
+        <v>123.99</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>-8.19</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>12.5</v>
+        <v>5.51</v>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
@@ -6191,13 +6191,13 @@
         </is>
       </c>
       <c r="L88" s="3" t="n">
-        <v>5.2</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="M88" s="3" t="n">
-        <v>12.92</v>
+        <v>6.45</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>-12.74</v>
+        <v>-6.9802</v>
       </c>
       <c r="O88" s="3" t="n">
         <v>0</v>
@@ -6212,7 +6212,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>CGAS5</t>
+          <t>EQTL3</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -6221,19 +6221,19 @@
         </is>
       </c>
       <c r="C89" s="3" t="n">
-        <v>33.9</v>
+        <v>45.2</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>135.3</v>
+        <v>42.11</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>123.99</v>
+        <v>38.55</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>-8.359999999999999</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>5.51</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
@@ -6256,13 +6256,13 @@
         </is>
       </c>
       <c r="L89" s="3" t="n">
-        <v>8.220000000000001</v>
+        <v>2.52</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>6.45</v>
+        <v>6.33</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>-6.9802</v>
+        <v>-1.4698</v>
       </c>
       <c r="O89" s="3" t="n">
         <v>0</v>
@@ -6277,7 +6277,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>EQTL3</t>
+          <t>FLRY3</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -6289,16 +6289,16 @@
         <v>45.2</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>42.11</v>
+        <v>16.82</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>38.55</v>
+        <v>15.39</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>-8.449999999999999</v>
+        <v>-8.5</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>8.960000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
@@ -6321,13 +6321,13 @@
         </is>
       </c>
       <c r="L90" s="3" t="n">
-        <v>2.52</v>
+        <v>1.31</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>6.33</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>-1.4698</v>
+        <v>-6.2504</v>
       </c>
       <c r="O90" s="3" t="n">
         <v>0</v>
@@ -6342,7 +6342,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>FLRY3</t>
+          <t>ITSA4</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -6351,19 +6351,19 @@
         </is>
       </c>
       <c r="C91" s="3" t="n">
-        <v>45.2</v>
+        <v>41.9</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>16.82</v>
+        <v>14.12</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>15.39</v>
+        <v>12.92</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>-8.5</v>
+        <v>-8.52</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>14.74</v>
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
@@ -6386,13 +6386,13 @@
         </is>
       </c>
       <c r="L91" s="3" t="n">
-        <v>1.31</v>
+        <v>0.98</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>8.279999999999999</v>
+        <v>7.36</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-6.2504</v>
+        <v>-3.3226</v>
       </c>
       <c r="O91" s="3" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>ITSA4</t>
+          <t>SBSP3</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -6416,19 +6416,19 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>41.9</v>
+        <v>45.2</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>14.12</v>
+        <v>30.56</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>12.92</v>
+        <v>27.95</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>-8.52</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>14.74</v>
+        <v>11.2</v>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
@@ -6451,13 +6451,13 @@
         </is>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0.98</v>
+        <v>1.82</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>7.36</v>
+        <v>5.86</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>-3.3226</v>
+        <v>-0.2069</v>
       </c>
       <c r="O92" s="3" t="n">
         <v>0</v>
@@ -6472,7 +6472,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>SBSP3</t>
+          <t>TTEN3</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -6481,19 +6481,19 @@
         </is>
       </c>
       <c r="C93" s="3" t="n">
-        <v>45.2</v>
+        <v>46.8</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>30.56</v>
+        <v>17.11</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>27.95</v>
+        <v>15.6</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>-8.539999999999999</v>
+        <v>-8.83</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>11.2</v>
+        <v>9.01</v>
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
@@ -6516,13 +6516,13 @@
         </is>
       </c>
       <c r="L93" s="3" t="n">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="M93" s="3" t="n">
-        <v>5.86</v>
+        <v>10.35</v>
       </c>
       <c r="N93" s="3" t="n">
-        <v>-0.2069</v>
+        <v>-5.4918</v>
       </c>
       <c r="O93" s="3" t="n">
         <v>0</v>
@@ -6537,7 +6537,7 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>TTEN3</t>
+          <t>UCAS3</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -6546,19 +6546,19 @@
         </is>
       </c>
       <c r="C94" s="3" t="n">
-        <v>46.8</v>
+        <v>43.5</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>17.11</v>
+        <v>1.46</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>15.6</v>
+        <v>1.32</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>-8.83</v>
+        <v>-9.59</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>9.01</v>
+        <v>2.77</v>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
@@ -6581,13 +6581,13 @@
         </is>
       </c>
       <c r="L94" s="3" t="n">
-        <v>1.64</v>
+        <v>0.09</v>
       </c>
       <c r="M94" s="3" t="n">
-        <v>10.35</v>
+        <v>5.99</v>
       </c>
       <c r="N94" s="3" t="n">
-        <v>-5.4918</v>
+        <v>-0.3477</v>
       </c>
       <c r="O94" s="3" t="n">
         <v>0</v>
@@ -6602,7 +6602,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>UCAS3</t>
+          <t>ABCB4</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -6611,19 +6611,19 @@
         </is>
       </c>
       <c r="C95" s="3" t="n">
-        <v>43.5</v>
+        <v>41.9</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>1.46</v>
+        <v>27.13</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>1.32</v>
+        <v>24.5</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>-9.59</v>
+        <v>-9.69</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>2.77</v>
+        <v>11.79</v>
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
@@ -6646,13 +6646,13 @@
         </is>
       </c>
       <c r="L95" s="3" t="n">
-        <v>0.09</v>
+        <v>2.47</v>
       </c>
       <c r="M95" s="3" t="n">
-        <v>5.99</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="N95" s="3" t="n">
-        <v>-0.3477</v>
+        <v>-7.374</v>
       </c>
       <c r="O95" s="3" t="n">
         <v>0</v>
@@ -6667,7 +6667,7 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>ABCB4</t>
+          <t>NEXP3</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -6676,23 +6676,23 @@
         </is>
       </c>
       <c r="C96" s="3" t="n">
-        <v>41.9</v>
+        <v>29</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>27.13</v>
+        <v>2.78</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>24.5</v>
+        <v>2.5</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>-9.69</v>
+        <v>-10.07</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>11.79</v>
+        <v>-15.7</v>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="I96" s="3" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="K96" s="3" t="inlineStr">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="L96" s="3" t="n">
-        <v>2.47</v>
+        <v>0.18</v>
       </c>
       <c r="M96" s="3" t="n">
-        <v>9.960000000000001</v>
+        <v>6.52</v>
       </c>
       <c r="N96" s="3" t="n">
-        <v>-7.374</v>
+        <v>-2.7281</v>
       </c>
       <c r="O96" s="3" t="n">
         <v>0</v>
@@ -6732,28 +6732,28 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>NEXP3</t>
+          <t>CEAB3</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Não Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="C97" s="3" t="n">
-        <v>29</v>
+        <v>53.2</v>
       </c>
       <c r="D97" s="3" t="n">
-        <v>2.78</v>
+        <v>12.94</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>2.5</v>
+        <v>11.58</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>-10.07</v>
+        <v>-10.51</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>-15.7</v>
+        <v>-18.87</v>
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
@@ -6776,13 +6776,13 @@
         </is>
       </c>
       <c r="L97" s="3" t="n">
-        <v>0.18</v>
+        <v>1.1</v>
       </c>
       <c r="M97" s="3" t="n">
-        <v>6.52</v>
+        <v>9.09</v>
       </c>
       <c r="N97" s="3" t="n">
-        <v>-2.7281</v>
+        <v>-2.2549</v>
       </c>
       <c r="O97" s="3" t="n">
         <v>0</v>
@@ -6797,32 +6797,32 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>CEAB3</t>
+          <t>IGTI11</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Não Previsível</t>
         </is>
       </c>
       <c r="C98" s="3" t="n">
-        <v>53.2</v>
+        <v>41.9</v>
       </c>
       <c r="D98" s="3" t="n">
-        <v>12.94</v>
+        <v>29.05</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>11.58</v>
+        <v>25.94</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>-10.51</v>
+        <v>-10.71</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>-18.87</v>
+        <v>10.92</v>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="I98" s="3" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="K98" s="3" t="inlineStr">
@@ -6841,13 +6841,13 @@
         </is>
       </c>
       <c r="L98" s="3" t="n">
-        <v>1.1</v>
+        <v>2.45</v>
       </c>
       <c r="M98" s="3" t="n">
         <v>9.09</v>
       </c>
       <c r="N98" s="3" t="n">
-        <v>-2.2549</v>
+        <v>-5.0659</v>
       </c>
       <c r="O98" s="3" t="n">
         <v>0</v>
@@ -6862,32 +6862,32 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>IGTI11</t>
+          <t>POMO4</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Não Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="C99" s="3" t="n">
-        <v>41.9</v>
+        <v>56.5</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>29.05</v>
+        <v>6.79</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>25.94</v>
+        <v>6.06</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>-10.71</v>
+        <v>-10.79</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>10.92</v>
+        <v>-11.1</v>
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="I99" s="3" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="K99" s="3" t="inlineStr">
@@ -6906,13 +6906,13 @@
         </is>
       </c>
       <c r="L99" s="3" t="n">
-        <v>2.45</v>
+        <v>0.82</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>9.09</v>
+        <v>12.88</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>-5.0659</v>
+        <v>-7.0248</v>
       </c>
       <c r="O99" s="3" t="n">
         <v>0</v>
@@ -6927,32 +6927,32 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>POMO4</t>
+          <t>ENGI11</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Não Previsível</t>
         </is>
       </c>
       <c r="C100" s="3" t="n">
-        <v>56.5</v>
+        <v>43.5</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>6.79</v>
+        <v>53.85</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>6.06</v>
+        <v>48</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>-10.79</v>
+        <v>-10.86</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>-11.1</v>
+        <v>8.84</v>
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="I100" s="3" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="K100" s="3" t="inlineStr">
@@ -6971,13 +6971,13 @@
         </is>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0.82</v>
+        <v>3.21</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>12.88</v>
+        <v>6.32</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>-7.0248</v>
+        <v>-0.9977</v>
       </c>
       <c r="O100" s="3" t="n">
         <v>0</v>
@@ -6992,32 +6992,32 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>ENGI11</t>
+          <t>SCAR3</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Não Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="C101" s="3" t="n">
-        <v>43.5</v>
+        <v>56.5</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>53.85</v>
+        <v>15.29</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>48</v>
+        <v>13.6</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>-10.86</v>
+        <v>-11.05</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>8.84</v>
+        <v>-0.49</v>
       </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="I101" s="3" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="K101" s="3" t="inlineStr">
@@ -7036,13 +7036,13 @@
         </is>
       </c>
       <c r="L101" s="3" t="n">
-        <v>3.21</v>
+        <v>0.7</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>6.32</v>
+        <v>5.05</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>-0.9977</v>
+        <v>-1.1913</v>
       </c>
       <c r="O101" s="3" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>SHUL4</t>
+          <t>WEGE3</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -7069,16 +7069,16 @@
         <v>43.5</v>
       </c>
       <c r="D102" s="3" t="n">
-        <v>5.54</v>
+        <v>49.59</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>4.93</v>
+        <v>44.1</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>-10.97</v>
+        <v>-11.07</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>16.63</v>
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
@@ -7101,13 +7101,13 @@
         </is>
       </c>
       <c r="L102" s="3" t="n">
-        <v>0.29</v>
+        <v>10.04</v>
       </c>
       <c r="M102" s="3" t="n">
-        <v>5.78</v>
+        <v>22.14</v>
       </c>
       <c r="N102" s="3" t="n">
-        <v>-4.7938</v>
+        <v>-13.7967</v>
       </c>
       <c r="O102" s="3" t="n">
         <v>0</v>
@@ -7122,32 +7122,32 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>SCAR3</t>
+          <t>ALOS3</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Não Previsível</t>
         </is>
       </c>
       <c r="C103" s="3" t="n">
-        <v>56.5</v>
+        <v>48.4</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>15.29</v>
+        <v>31.74</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>13.6</v>
+        <v>28.21</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>-11.05</v>
+        <v>-11.13</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>-0.49</v>
+        <v>14.93</v>
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="I103" s="3" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="K103" s="3" t="inlineStr">
@@ -7166,13 +7166,13 @@
         </is>
       </c>
       <c r="L103" s="3" t="n">
-        <v>0.7</v>
+        <v>2.86</v>
       </c>
       <c r="M103" s="3" t="n">
-        <v>5.05</v>
+        <v>9.83</v>
       </c>
       <c r="N103" s="3" t="n">
-        <v>-1.1913</v>
+        <v>-4.7845</v>
       </c>
       <c r="O103" s="3" t="n">
         <v>0</v>
@@ -7187,7 +7187,7 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>WEGE3</t>
+          <t>CMIN3</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -7196,19 +7196,19 @@
         </is>
       </c>
       <c r="C104" s="3" t="n">
-        <v>43.5</v>
+        <v>46.8</v>
       </c>
       <c r="D104" s="3" t="n">
-        <v>49.59</v>
+        <v>5.28</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>44.1</v>
+        <v>4.66</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>-11.07</v>
+        <v>-11.82</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>16.63</v>
+        <v>7.73</v>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
@@ -7231,13 +7231,13 @@
         </is>
       </c>
       <c r="L104" s="3" t="n">
-        <v>10.04</v>
+        <v>1.15</v>
       </c>
       <c r="M104" s="3" t="n">
-        <v>22.14</v>
+        <v>24.37</v>
       </c>
       <c r="N104" s="3" t="n">
-        <v>-13.7967</v>
+        <v>-30.2966</v>
       </c>
       <c r="O104" s="3" t="n">
         <v>0</v>
@@ -7252,32 +7252,32 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>ALOS3</t>
+          <t>TOTS3</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Não Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="C105" s="3" t="n">
-        <v>48.4</v>
+        <v>54.8</v>
       </c>
       <c r="D105" s="3" t="n">
-        <v>31.74</v>
+        <v>37.65</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>28.21</v>
+        <v>33.07</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>-11.13</v>
+        <v>-12.16</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>14.93</v>
+        <v>-0.95</v>
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="I105" s="3" t="inlineStr">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="K105" s="3" t="inlineStr">
@@ -7296,13 +7296,13 @@
         </is>
       </c>
       <c r="L105" s="3" t="n">
-        <v>2.86</v>
+        <v>8.23</v>
       </c>
       <c r="M105" s="3" t="n">
-        <v>9.83</v>
+        <v>24.58</v>
       </c>
       <c r="N105" s="3" t="n">
-        <v>-4.7845</v>
+        <v>-19.9576</v>
       </c>
       <c r="O105" s="3" t="n">
         <v>0</v>
@@ -7317,7 +7317,7 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>CMIN3</t>
+          <t>AGRO3</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -7326,19 +7326,19 @@
         </is>
       </c>
       <c r="C106" s="3" t="n">
-        <v>46.8</v>
+        <v>40.3</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>5.28</v>
+        <v>21.38</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>4.66</v>
+        <v>18.78</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-11.82</v>
+        <v>-12.16</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>7.73</v>
+        <v>2.55</v>
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
@@ -7361,13 +7361,13 @@
         </is>
       </c>
       <c r="L106" s="3" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>24.37</v>
+        <v>6.26</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>-30.2966</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="O106" s="3" t="n">
         <v>0</v>
@@ -7382,32 +7382,32 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>TOTS3</t>
+          <t>DXCO3</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Não Previsível</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
-        <v>54.8</v>
+        <v>43.5</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>37.65</v>
+        <v>5.42</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>33.07</v>
+        <v>4.76</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>-12.16</v>
+        <v>-12.18</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>-0.95</v>
+        <v>4.3</v>
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="I107" s="3" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="K107" s="3" t="inlineStr">
@@ -7426,13 +7426,13 @@
         </is>
       </c>
       <c r="L107" s="3" t="n">
-        <v>8.23</v>
+        <v>0.47</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>24.58</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>-19.9576</v>
+        <v>-1.025</v>
       </c>
       <c r="O107" s="3" t="n">
         <v>0</v>
@@ -7447,7 +7447,7 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>AGRO3</t>
+          <t>BPAC11</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -7456,19 +7456,19 @@
         </is>
       </c>
       <c r="C108" s="3" t="n">
-        <v>40.3</v>
+        <v>43.5</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>21.38</v>
+        <v>61.26</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>18.78</v>
+        <v>53.75</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>-12.16</v>
+        <v>-12.26</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>2.55</v>
+        <v>14.74</v>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
@@ -7491,13 +7491,13 @@
         </is>
       </c>
       <c r="L108" s="3" t="n">
-        <v>1.23</v>
+        <v>7.54</v>
       </c>
       <c r="M108" s="3" t="n">
-        <v>6.26</v>
+        <v>13.44</v>
       </c>
       <c r="N108" s="3" t="n">
-        <v>-0.6294999999999999</v>
+        <v>-6.4324</v>
       </c>
       <c r="O108" s="3" t="n">
         <v>0</v>
@@ -7512,7 +7512,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>DXCO3</t>
+          <t>WIZC3</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -7521,19 +7521,19 @@
         </is>
       </c>
       <c r="C109" s="3" t="n">
-        <v>43.5</v>
+        <v>46.8</v>
       </c>
       <c r="D109" s="3" t="n">
-        <v>5.42</v>
+        <v>8.98</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>4.76</v>
+        <v>7.85</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>-12.18</v>
+        <v>-12.58</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>4.3</v>
+        <v>9.66</v>
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
@@ -7556,13 +7556,13 @@
         </is>
       </c>
       <c r="L109" s="3" t="n">
-        <v>0.47</v>
+        <v>0.92</v>
       </c>
       <c r="M109" s="3" t="n">
-        <v>9.609999999999999</v>
+        <v>11.11</v>
       </c>
       <c r="N109" s="3" t="n">
-        <v>-1.025</v>
+        <v>-4.5586</v>
       </c>
       <c r="O109" s="3" t="n">
         <v>0</v>
@@ -7577,32 +7577,32 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>BPAC11</t>
+          <t>RAIL3</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Não Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="C110" s="3" t="n">
-        <v>43.5</v>
+        <v>67.7</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>61.26</v>
+        <v>15.86</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>53.75</v>
+        <v>13.72</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>-12.26</v>
+        <v>-13.49</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>14.74</v>
+        <v>-0.64</v>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="I110" s="3" t="inlineStr">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="K110" s="3" t="inlineStr">
@@ -7621,13 +7621,13 @@
         </is>
       </c>
       <c r="L110" s="3" t="n">
-        <v>7.54</v>
+        <v>0.86</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>13.44</v>
+        <v>5.42</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>-6.4324</v>
+        <v>-0.6167</v>
       </c>
       <c r="O110" s="3" t="n">
         <v>0</v>
@@ -7642,7 +7642,7 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>WIZC3</t>
+          <t>ITUB4</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -7651,19 +7651,19 @@
         </is>
       </c>
       <c r="C111" s="3" t="n">
-        <v>46.8</v>
+        <v>45.2</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>8.98</v>
+        <v>46.34</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>7.85</v>
+        <v>40.04</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>-12.58</v>
+        <v>-13.59</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>9.66</v>
+        <v>13.16</v>
       </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
@@ -7686,13 +7686,13 @@
         </is>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0.92</v>
+        <v>4.73</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>11.11</v>
+        <v>11.44</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>-4.5586</v>
+        <v>-5.9983</v>
       </c>
       <c r="O111" s="3" t="n">
         <v>0</v>
@@ -7707,32 +7707,32 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>RAIL3</t>
+          <t>UNIP6</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Não Previsível</t>
         </is>
       </c>
       <c r="C112" s="3" t="n">
-        <v>67.7</v>
+        <v>50</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>15.86</v>
+        <v>70.5</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>13.72</v>
+        <v>60.91</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>-13.49</v>
+        <v>-13.6</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>-0.64</v>
+        <v>5.63</v>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="I112" s="3" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="K112" s="3" t="inlineStr">
@@ -7751,13 +7751,13 @@
         </is>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0.86</v>
+        <v>4.71</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>5.42</v>
+        <v>7.58</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>-0.6167</v>
+        <v>-1.5003</v>
       </c>
       <c r="O112" s="3" t="n">
         <v>0</v>
@@ -7772,7 +7772,7 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>ITUB4</t>
+          <t>BBDC3</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -7781,19 +7781,19 @@
         </is>
       </c>
       <c r="C113" s="3" t="n">
-        <v>45.2</v>
+        <v>43.5</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>46.34</v>
+        <v>18.02</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>40.04</v>
+        <v>15.5</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>-13.59</v>
+        <v>-13.99</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>13.16</v>
+        <v>12.7</v>
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
@@ -7816,13 +7816,13 @@
         </is>
       </c>
       <c r="L113" s="3" t="n">
-        <v>4.73</v>
+        <v>2.34</v>
       </c>
       <c r="M113" s="3" t="n">
-        <v>11.44</v>
+        <v>14.58</v>
       </c>
       <c r="N113" s="3" t="n">
-        <v>-5.9983</v>
+        <v>-8.873699999999999</v>
       </c>
       <c r="O113" s="3" t="n">
         <v>0</v>
@@ -7837,7 +7837,7 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>UNIP6</t>
+          <t>AXIA3</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -7846,19 +7846,19 @@
         </is>
       </c>
       <c r="C114" s="3" t="n">
-        <v>50</v>
+        <v>43.5</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>70.5</v>
+        <v>61.27</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>60.91</v>
+        <v>52.43</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>-13.6</v>
+        <v>-14.43</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>5.63</v>
+        <v>14.05</v>
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
@@ -7881,13 +7881,13 @@
         </is>
       </c>
       <c r="L114" s="3" t="n">
-        <v>4.71</v>
+        <v>7.72</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>7.58</v>
+        <v>13.58</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>-1.5003</v>
+        <v>-5.4348</v>
       </c>
       <c r="O114" s="3" t="n">
         <v>0</v>
@@ -7902,7 +7902,7 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>BBDC3</t>
+          <t>JALL3</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -7911,19 +7911,19 @@
         </is>
       </c>
       <c r="C115" s="3" t="n">
-        <v>43.5</v>
+        <v>37.1</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>18.02</v>
+        <v>3.04</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>15.5</v>
+        <v>2.6</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>-13.99</v>
+        <v>-14.47</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>12.7</v>
+        <v>0.44</v>
       </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
@@ -7946,13 +7946,13 @@
         </is>
       </c>
       <c r="L115" s="3" t="n">
-        <v>2.34</v>
+        <v>0.32</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>14.58</v>
+        <v>9.6</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>-8.873699999999999</v>
+        <v>-1.0299</v>
       </c>
       <c r="O115" s="3" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>AXIA3</t>
+          <t>MULT3</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -7979,16 +7979,16 @@
         <v>43.5</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>61.27</v>
+        <v>34.87</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>52.43</v>
+        <v>29.79</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>-14.43</v>
+        <v>-14.57</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>14.05</v>
+        <v>9.02</v>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="L116" s="3" t="n">
-        <v>7.72</v>
+        <v>2.03</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>13.58</v>
+        <v>6.58</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>-5.4348</v>
+        <v>-1.5381</v>
       </c>
       <c r="O116" s="3" t="n">
         <v>0</v>
@@ -8032,7 +8032,7 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>JALL3</t>
+          <t>TFCO4</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -8041,19 +8041,19 @@
         </is>
       </c>
       <c r="C117" s="3" t="n">
-        <v>37.1</v>
+        <v>38.7</v>
       </c>
       <c r="D117" s="3" t="n">
-        <v>3.04</v>
+        <v>17.36</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>2.6</v>
+        <v>14.83</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>-14.47</v>
+        <v>-14.6</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>0.44</v>
+        <v>2.36</v>
       </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
@@ -8076,13 +8076,13 @@
         </is>
       </c>
       <c r="L117" s="3" t="n">
-        <v>0.32</v>
+        <v>1.21</v>
       </c>
       <c r="M117" s="3" t="n">
-        <v>9.6</v>
+        <v>7.88</v>
       </c>
       <c r="N117" s="3" t="n">
-        <v>-1.0299</v>
+        <v>-3.1988</v>
       </c>
       <c r="O117" s="3" t="n">
         <v>0</v>
@@ -8097,7 +8097,7 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>MULT3</t>
+          <t>MDNE3</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -8106,19 +8106,19 @@
         </is>
       </c>
       <c r="C118" s="3" t="n">
-        <v>43.5</v>
+        <v>46.8</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>34.87</v>
+        <v>32.95</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>29.79</v>
+        <v>28.11</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>-14.57</v>
+        <v>-14.69</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>9.02</v>
+        <v>14.93</v>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
@@ -8141,13 +8141,13 @@
         </is>
       </c>
       <c r="L118" s="3" t="n">
-        <v>2.03</v>
+        <v>2.47</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>6.58</v>
+        <v>8.33</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>-1.5381</v>
+        <v>-1.4346</v>
       </c>
       <c r="O118" s="3" t="n">
         <v>0</v>
@@ -8162,7 +8162,7 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>TFCO4</t>
+          <t>BBDC4</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -8171,19 +8171,19 @@
         </is>
       </c>
       <c r="C119" s="3" t="n">
-        <v>38.7</v>
+        <v>45.2</v>
       </c>
       <c r="D119" s="3" t="n">
-        <v>17.36</v>
+        <v>20.76</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>14.83</v>
+        <v>17.7</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>-14.6</v>
+        <v>-14.76</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>2.36</v>
+        <v>12.43</v>
       </c>
       <c r="H119" s="3" t="inlineStr">
         <is>
@@ -8206,13 +8206,13 @@
         </is>
       </c>
       <c r="L119" s="3" t="n">
-        <v>1.21</v>
+        <v>2.85</v>
       </c>
       <c r="M119" s="3" t="n">
-        <v>7.88</v>
+        <v>15.4</v>
       </c>
       <c r="N119" s="3" t="n">
-        <v>-3.1988</v>
+        <v>-8.7895</v>
       </c>
       <c r="O119" s="3" t="n">
         <v>0</v>
@@ -8227,32 +8227,32 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>MDNE3</t>
+          <t>MYPK3</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>Não Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="C120" s="3" t="n">
-        <v>46.8</v>
+        <v>58.1</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>32.95</v>
+        <v>10.55</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>28.11</v>
+        <v>8.98</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>-14.69</v>
+        <v>-14.88</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>14.93</v>
+        <v>-18.68</v>
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="I120" s="3" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="K120" s="3" t="inlineStr">
@@ -8271,13 +8271,13 @@
         </is>
       </c>
       <c r="L120" s="3" t="n">
-        <v>2.47</v>
+        <v>1.06</v>
       </c>
       <c r="M120" s="3" t="n">
-        <v>8.33</v>
+        <v>11.06</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>-1.4346</v>
+        <v>-6.5872</v>
       </c>
       <c r="O120" s="3" t="n">
         <v>0</v>
@@ -8292,7 +8292,7 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>BBDC4</t>
+          <t>MOTV3</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -8301,19 +8301,19 @@
         </is>
       </c>
       <c r="C121" s="3" t="n">
-        <v>45.2</v>
+        <v>35.5</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>20.76</v>
+        <v>16.59</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>17.7</v>
+        <v>14.11</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>-14.76</v>
+        <v>-14.95</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>12.43</v>
+        <v>9.52</v>
       </c>
       <c r="H121" s="3" t="inlineStr">
         <is>
@@ -8336,13 +8336,13 @@
         </is>
       </c>
       <c r="L121" s="3" t="n">
-        <v>2.85</v>
+        <v>2.03</v>
       </c>
       <c r="M121" s="3" t="n">
-        <v>15.4</v>
+        <v>13.3</v>
       </c>
       <c r="N121" s="3" t="n">
-        <v>-8.7895</v>
+        <v>-6.3539</v>
       </c>
       <c r="O121" s="3" t="n">
         <v>0</v>
@@ -8357,32 +8357,32 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>MYPK3</t>
+          <t>IRBR3</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Não Previsível</t>
         </is>
       </c>
       <c r="C122" s="3" t="n">
-        <v>58.1</v>
+        <v>43.5</v>
       </c>
       <c r="D122" s="3" t="n">
-        <v>10.55</v>
+        <v>60.84</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>8.98</v>
+        <v>51.6</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>-14.88</v>
+        <v>-15.19</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>-18.68</v>
+        <v>10.21</v>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="I122" s="3" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="K122" s="3" t="inlineStr">
@@ -8401,13 +8401,13 @@
         </is>
       </c>
       <c r="L122" s="3" t="n">
-        <v>1.06</v>
+        <v>5.56</v>
       </c>
       <c r="M122" s="3" t="n">
-        <v>11.06</v>
+        <v>10.42</v>
       </c>
       <c r="N122" s="3" t="n">
-        <v>-6.5872</v>
+        <v>-7.8708</v>
       </c>
       <c r="O122" s="3" t="n">
         <v>0</v>
@@ -8422,7 +8422,7 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>MOTV3</t>
+          <t>RDOR3</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -8431,19 +8431,19 @@
         </is>
       </c>
       <c r="C123" s="3" t="n">
-        <v>35.5</v>
+        <v>51.6</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>16.59</v>
+        <v>40.13</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>14.11</v>
+        <v>34.02</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>-14.95</v>
+        <v>-15.23</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>9.52</v>
+        <v>10.67</v>
       </c>
       <c r="H123" s="3" t="inlineStr">
         <is>
@@ -8466,13 +8466,13 @@
         </is>
       </c>
       <c r="L123" s="3" t="n">
-        <v>2.03</v>
+        <v>9.09</v>
       </c>
       <c r="M123" s="3" t="n">
-        <v>13.3</v>
+        <v>24.53</v>
       </c>
       <c r="N123" s="3" t="n">
-        <v>-6.3539</v>
+        <v>-20.1299</v>
       </c>
       <c r="O123" s="3" t="n">
         <v>0</v>
@@ -8487,7 +8487,7 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>IRBR3</t>
+          <t>SAPR11</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -8496,19 +8496,19 @@
         </is>
       </c>
       <c r="C124" s="3" t="n">
-        <v>43.5</v>
+        <v>40.3</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>60.84</v>
+        <v>45.1</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>51.6</v>
+        <v>37.94</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>-15.19</v>
+        <v>-15.88</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>10.21</v>
+        <v>13.16</v>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
@@ -8531,13 +8531,13 @@
         </is>
       </c>
       <c r="L124" s="3" t="n">
-        <v>5.56</v>
+        <v>6.13</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>10.42</v>
+        <v>15.21</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>-7.8708</v>
+        <v>-8.0761</v>
       </c>
       <c r="O124" s="3" t="n">
         <v>0</v>
@@ -8552,7 +8552,7 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>RDOR3</t>
+          <t>MELK3</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -8561,19 +8561,19 @@
         </is>
       </c>
       <c r="C125" s="3" t="n">
-        <v>51.6</v>
+        <v>38.7</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>40.13</v>
+        <v>3.91</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>34.02</v>
+        <v>3.28</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>-15.23</v>
+        <v>-16.12</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>10.67</v>
+        <v>7.66</v>
       </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
@@ -8596,13 +8596,13 @@
         </is>
       </c>
       <c r="L125" s="3" t="n">
-        <v>9.09</v>
+        <v>0.58</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>24.53</v>
+        <v>17.43</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>-20.1299</v>
+        <v>-13.572</v>
       </c>
       <c r="O125" s="3" t="n">
         <v>0</v>
@@ -8617,7 +8617,7 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>SAPR11</t>
+          <t>EZTC3</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -8626,19 +8626,19 @@
         </is>
       </c>
       <c r="C126" s="3" t="n">
-        <v>40.3</v>
+        <v>45.2</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>45.1</v>
+        <v>15.68</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>37.94</v>
+        <v>13.15</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>-15.88</v>
+        <v>-16.13</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>13.16</v>
+        <v>15.14</v>
       </c>
       <c r="H126" s="3" t="inlineStr">
         <is>
@@ -8661,13 +8661,13 @@
         </is>
       </c>
       <c r="L126" s="3" t="n">
-        <v>6.13</v>
+        <v>3.3</v>
       </c>
       <c r="M126" s="3" t="n">
-        <v>15.21</v>
+        <v>24.12</v>
       </c>
       <c r="N126" s="3" t="n">
-        <v>-8.0761</v>
+        <v>-14.1551</v>
       </c>
       <c r="O126" s="3" t="n">
         <v>0</v>
@@ -8682,7 +8682,7 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>MELK3</t>
+          <t>RENT3</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -8694,16 +8694,16 @@
         <v>38.7</v>
       </c>
       <c r="D127" s="3" t="n">
-        <v>3.91</v>
+        <v>50.17</v>
       </c>
       <c r="E127" s="3" t="n">
-        <v>3.28</v>
+        <v>42.02</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>-16.12</v>
+        <v>-16.25</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>7.66</v>
+        <v>14.83</v>
       </c>
       <c r="H127" s="3" t="inlineStr">
         <is>
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L127" s="3" t="n">
-        <v>0.58</v>
+        <v>6.56</v>
       </c>
       <c r="M127" s="3" t="n">
-        <v>17.43</v>
+        <v>14.56</v>
       </c>
       <c r="N127" s="3" t="n">
-        <v>-13.572</v>
+        <v>-6.7578</v>
       </c>
       <c r="O127" s="3" t="n">
         <v>0</v>
@@ -8747,7 +8747,7 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>EZTC3</t>
+          <t>CAML3</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -8756,19 +8756,19 @@
         </is>
       </c>
       <c r="C128" s="3" t="n">
-        <v>45.2</v>
+        <v>40.3</v>
       </c>
       <c r="D128" s="3" t="n">
-        <v>15.68</v>
+        <v>6.81</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>13.15</v>
+        <v>5.7</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>-16.13</v>
+        <v>-16.26</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>15.14</v>
+        <v>15.31</v>
       </c>
       <c r="H128" s="3" t="inlineStr">
         <is>
@@ -8791,13 +8791,13 @@
         </is>
       </c>
       <c r="L128" s="3" t="n">
-        <v>3.3</v>
+        <v>0.88</v>
       </c>
       <c r="M128" s="3" t="n">
-        <v>24.12</v>
+        <v>14.74</v>
       </c>
       <c r="N128" s="3" t="n">
-        <v>-14.1551</v>
+        <v>-3.8213</v>
       </c>
       <c r="O128" s="3" t="n">
         <v>0</v>
@@ -8812,32 +8812,32 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>RENT3</t>
+          <t>HBOR3</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>Não Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="C129" s="3" t="n">
-        <v>38.7</v>
+        <v>53.2</v>
       </c>
       <c r="D129" s="3" t="n">
-        <v>50.17</v>
+        <v>3.04</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>42.02</v>
+        <v>2.54</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>-16.25</v>
+        <v>-16.4</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>14.83</v>
+        <v>-8.74</v>
       </c>
       <c r="H129" s="3" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="I129" s="3" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="K129" s="3" t="inlineStr">
@@ -8856,13 +8856,13 @@
         </is>
       </c>
       <c r="L129" s="3" t="n">
-        <v>6.56</v>
+        <v>0.22</v>
       </c>
       <c r="M129" s="3" t="n">
-        <v>14.56</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="N129" s="3" t="n">
-        <v>-6.7578</v>
+        <v>0.0546</v>
       </c>
       <c r="O129" s="3" t="n">
         <v>0</v>
@@ -8877,32 +8877,32 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>CAML3</t>
+          <t>MDIA3</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>Não Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="C130" s="3" t="n">
-        <v>40.3</v>
+        <v>58.1</v>
       </c>
       <c r="D130" s="3" t="n">
-        <v>6.81</v>
+        <v>23.3</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>5.7</v>
+        <v>19.39</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>-16.26</v>
+        <v>-16.79</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>15.31</v>
+        <v>-4.94</v>
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="I130" s="3" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="K130" s="3" t="inlineStr">
@@ -8921,13 +8921,13 @@
         </is>
       </c>
       <c r="L130" s="3" t="n">
-        <v>0.88</v>
+        <v>1.74</v>
       </c>
       <c r="M130" s="3" t="n">
-        <v>14.74</v>
+        <v>8.26</v>
       </c>
       <c r="N130" s="3" t="n">
-        <v>-3.8213</v>
+        <v>-1.0808</v>
       </c>
       <c r="O130" s="3" t="n">
         <v>0</v>
@@ -8942,28 +8942,28 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>HBOR3</t>
+          <t>RPMG3</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Não Previsível</t>
         </is>
       </c>
       <c r="C131" s="3" t="n">
-        <v>53.2</v>
+        <v>46.8</v>
       </c>
       <c r="D131" s="3" t="n">
-        <v>3.04</v>
+        <v>2.25</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>2.54</v>
+        <v>1.87</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>-16.4</v>
+        <v>-16.89</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>-8.74</v>
+        <v>-22.06</v>
       </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
@@ -8986,13 +8986,13 @@
         </is>
       </c>
       <c r="L131" s="3" t="n">
-        <v>0.22</v>
+        <v>0.46</v>
       </c>
       <c r="M131" s="3" t="n">
-        <v>9.359999999999999</v>
+        <v>21.5</v>
       </c>
       <c r="N131" s="3" t="n">
-        <v>0.0546</v>
+        <v>-20.9513</v>
       </c>
       <c r="O131" s="3" t="n">
         <v>0</v>
@@ -9007,32 +9007,32 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>MDIA3</t>
+          <t>CURY3</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Não Previsível</t>
         </is>
       </c>
       <c r="C132" s="3" t="n">
-        <v>58.1</v>
+        <v>41.9</v>
       </c>
       <c r="D132" s="3" t="n">
-        <v>23.3</v>
+        <v>38.2</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>19.39</v>
+        <v>31.73</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>-16.79</v>
+        <v>-16.93</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>-4.94</v>
+        <v>11</v>
       </c>
       <c r="H132" s="3" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="I132" s="3" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="K132" s="3" t="inlineStr">
@@ -9051,13 +9051,13 @@
         </is>
       </c>
       <c r="L132" s="3" t="n">
-        <v>1.74</v>
+        <v>5.13</v>
       </c>
       <c r="M132" s="3" t="n">
-        <v>8.26</v>
+        <v>16.34</v>
       </c>
       <c r="N132" s="3" t="n">
-        <v>-1.0808</v>
+        <v>-4.7696</v>
       </c>
       <c r="O132" s="3" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>RPMG3</t>
+          <t>GRND3</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -9081,23 +9081,23 @@
         </is>
       </c>
       <c r="C133" s="3" t="n">
-        <v>46.8</v>
+        <v>40.3</v>
       </c>
       <c r="D133" s="3" t="n">
-        <v>2.25</v>
+        <v>4.92</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>1.87</v>
+        <v>4.07</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>-16.89</v>
+        <v>-17.34</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>-22.06</v>
+        <v>8.98</v>
       </c>
       <c r="H133" s="3" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="I133" s="3" t="inlineStr">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="K133" s="3" t="inlineStr">
@@ -9116,13 +9116,13 @@
         </is>
       </c>
       <c r="L133" s="3" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="M133" s="3" t="n">
-        <v>21.5</v>
+        <v>10.6</v>
       </c>
       <c r="N133" s="3" t="n">
-        <v>-20.9513</v>
+        <v>-3.2135</v>
       </c>
       <c r="O133" s="3" t="n">
         <v>0</v>
@@ -9137,7 +9137,7 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>CURY3</t>
+          <t>AGXY3</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -9146,23 +9146,23 @@
         </is>
       </c>
       <c r="C134" s="3" t="n">
-        <v>41.9</v>
+        <v>40.3</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>38.2</v>
+        <v>2.24</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>31.73</v>
+        <v>1.85</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>-16.93</v>
+        <v>-17.41</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>11</v>
+        <v>-44.82</v>
       </c>
       <c r="H134" s="3" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="I134" s="3" t="inlineStr">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="K134" s="3" t="inlineStr">
@@ -9181,13 +9181,13 @@
         </is>
       </c>
       <c r="L134" s="3" t="n">
-        <v>5.13</v>
+        <v>0.46</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>16.34</v>
+        <v>21.38</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>-4.7696</v>
+        <v>-18.2931</v>
       </c>
       <c r="O134" s="3" t="n">
         <v>0</v>
@@ -9202,7 +9202,7 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>GRND3</t>
+          <t>SANB11</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -9211,19 +9211,19 @@
         </is>
       </c>
       <c r="C135" s="3" t="n">
-        <v>40.3</v>
+        <v>43.5</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>4.92</v>
+        <v>32.93</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>4.07</v>
+        <v>27.16</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-17.34</v>
+        <v>-17.53</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>8.98</v>
+        <v>13.57</v>
       </c>
       <c r="H135" s="3" t="inlineStr">
         <is>
@@ -9246,13 +9246,13 @@
         </is>
       </c>
       <c r="L135" s="3" t="n">
-        <v>0.44</v>
+        <v>8.59</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>10.6</v>
+        <v>29.69</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-3.2135</v>
+        <v>-28.5489</v>
       </c>
       <c r="O135" s="3" t="n">
         <v>0</v>
@@ -9267,7 +9267,7 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>AGXY3</t>
+          <t>DIRR3</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -9279,20 +9279,20 @@
         <v>40.3</v>
       </c>
       <c r="D136" s="3" t="n">
-        <v>2.24</v>
+        <v>16.32</v>
       </c>
       <c r="E136" s="3" t="n">
-        <v>1.85</v>
+        <v>13.4</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>-17.41</v>
+        <v>-17.89</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>-44.82</v>
+        <v>7.09</v>
       </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="I136" s="3" t="inlineStr">
@@ -9302,7 +9302,7 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="K136" s="3" t="inlineStr">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="L136" s="3" t="n">
-        <v>0.46</v>
+        <v>2.57</v>
       </c>
       <c r="M136" s="3" t="n">
-        <v>21.38</v>
+        <v>19.14</v>
       </c>
       <c r="N136" s="3" t="n">
-        <v>-18.2931</v>
+        <v>-9.9785</v>
       </c>
       <c r="O136" s="3" t="n">
         <v>0</v>
@@ -9332,32 +9332,32 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>SANB11</t>
+          <t>AERI3</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>Não Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="C137" s="3" t="n">
-        <v>43.5</v>
+        <v>56.5</v>
       </c>
       <c r="D137" s="3" t="n">
-        <v>32.93</v>
+        <v>2.79</v>
       </c>
       <c r="E137" s="3" t="n">
-        <v>27.16</v>
+        <v>2.29</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>-17.53</v>
+        <v>-17.92</v>
       </c>
       <c r="G137" s="3" t="n">
-        <v>13.57</v>
+        <v>-21.13</v>
       </c>
       <c r="H137" s="3" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="I137" s="3" t="inlineStr">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="K137" s="3" t="inlineStr">
@@ -9376,13 +9376,13 @@
         </is>
       </c>
       <c r="L137" s="3" t="n">
-        <v>8.59</v>
+        <v>0.19</v>
       </c>
       <c r="M137" s="3" t="n">
-        <v>29.69</v>
+        <v>7.42</v>
       </c>
       <c r="N137" s="3" t="n">
-        <v>-28.5489</v>
+        <v>-0.4267</v>
       </c>
       <c r="O137" s="3" t="n">
         <v>0</v>
@@ -9397,7 +9397,7 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>DIRR3</t>
+          <t>VIVT3</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -9406,19 +9406,19 @@
         </is>
       </c>
       <c r="C138" s="3" t="n">
-        <v>40.3</v>
+        <v>45.2</v>
       </c>
       <c r="D138" s="3" t="n">
-        <v>16.32</v>
+        <v>41.22</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>13.4</v>
+        <v>33.82</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>-17.89</v>
+        <v>-17.94</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>7.09</v>
+        <v>7.08</v>
       </c>
       <c r="H138" s="3" t="inlineStr">
         <is>
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L138" s="3" t="n">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="M138" s="3" t="n">
-        <v>19.14</v>
+        <v>7.69</v>
       </c>
       <c r="N138" s="3" t="n">
-        <v>-9.9785</v>
+        <v>-0.7738</v>
       </c>
       <c r="O138" s="3" t="n">
         <v>0</v>
@@ -9462,32 +9462,32 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>AERI3</t>
+          <t>VLID3</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Não Previsível</t>
         </is>
       </c>
       <c r="C139" s="3" t="n">
-        <v>56.5</v>
+        <v>37.1</v>
       </c>
       <c r="D139" s="3" t="n">
-        <v>2.79</v>
+        <v>21.6</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>2.29</v>
+        <v>17.63</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>-17.92</v>
+        <v>-18.39</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>-21.13</v>
+        <v>5.54</v>
       </c>
       <c r="H139" s="3" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="I139" s="3" t="inlineStr">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="K139" s="3" t="inlineStr">
@@ -9506,13 +9506,13 @@
         </is>
       </c>
       <c r="L139" s="3" t="n">
-        <v>0.19</v>
+        <v>3.02</v>
       </c>
       <c r="M139" s="3" t="n">
-        <v>7.42</v>
+        <v>16.22</v>
       </c>
       <c r="N139" s="3" t="n">
-        <v>-0.4267</v>
+        <v>-6.1955</v>
       </c>
       <c r="O139" s="3" t="n">
         <v>0</v>
@@ -9527,7 +9527,7 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>VIVT3</t>
+          <t>KLBN4</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -9536,19 +9536,19 @@
         </is>
       </c>
       <c r="C140" s="3" t="n">
-        <v>45.2</v>
+        <v>38.7</v>
       </c>
       <c r="D140" s="3" t="n">
-        <v>41.22</v>
+        <v>4.1</v>
       </c>
       <c r="E140" s="3" t="n">
-        <v>33.82</v>
+        <v>3.33</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>-17.94</v>
+        <v>-18.78</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>7.08</v>
+        <v>7.31</v>
       </c>
       <c r="H140" s="3" t="inlineStr">
         <is>
@@ -9571,13 +9571,13 @@
         </is>
       </c>
       <c r="L140" s="3" t="n">
-        <v>2.88</v>
+        <v>0.36</v>
       </c>
       <c r="M140" s="3" t="n">
-        <v>7.69</v>
+        <v>10.29</v>
       </c>
       <c r="N140" s="3" t="n">
-        <v>-0.7738</v>
+        <v>-2.587</v>
       </c>
       <c r="O140" s="3" t="n">
         <v>0</v>
@@ -9592,7 +9592,7 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>VLID3</t>
+          <t>KLBN11</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -9601,19 +9601,19 @@
         </is>
       </c>
       <c r="C141" s="3" t="n">
-        <v>37.1</v>
+        <v>38.7</v>
       </c>
       <c r="D141" s="3" t="n">
-        <v>21.6</v>
+        <v>20.56</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>17.63</v>
+        <v>16.67</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>-18.39</v>
+        <v>-18.92</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>5.54</v>
+        <v>7.21</v>
       </c>
       <c r="H141" s="3" t="inlineStr">
         <is>
@@ -9636,13 +9636,13 @@
         </is>
       </c>
       <c r="L141" s="3" t="n">
-        <v>3.02</v>
+        <v>1.82</v>
       </c>
       <c r="M141" s="3" t="n">
-        <v>16.22</v>
+        <v>10.5</v>
       </c>
       <c r="N141" s="3" t="n">
-        <v>-6.1955</v>
+        <v>-2.5535</v>
       </c>
       <c r="O141" s="3" t="n">
         <v>0</v>
@@ -9657,7 +9657,7 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>KLBN4</t>
+          <t>ALPA4</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -9666,19 +9666,19 @@
         </is>
       </c>
       <c r="C142" s="3" t="n">
-        <v>38.7</v>
+        <v>41.9</v>
       </c>
       <c r="D142" s="3" t="n">
-        <v>4.1</v>
+        <v>15.37</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>3.33</v>
+        <v>12.4</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>-18.78</v>
+        <v>-19.32</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>7.31</v>
+        <v>23.58</v>
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
@@ -9701,13 +9701,13 @@
         </is>
       </c>
       <c r="L142" s="3" t="n">
-        <v>0.36</v>
+        <v>4.06</v>
       </c>
       <c r="M142" s="3" t="n">
-        <v>10.29</v>
+        <v>33.9</v>
       </c>
       <c r="N142" s="3" t="n">
-        <v>-2.587</v>
+        <v>-29.4282</v>
       </c>
       <c r="O142" s="3" t="n">
         <v>0</v>
@@ -9722,7 +9722,7 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>KLBN11</t>
+          <t>TASA4</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -9734,16 +9734,16 @@
         <v>38.7</v>
       </c>
       <c r="D143" s="3" t="n">
-        <v>20.56</v>
+        <v>5.83</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>16.67</v>
+        <v>4.68</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>-18.92</v>
+        <v>-19.67</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>7.21</v>
+        <v>5.31</v>
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
@@ -9766,13 +9766,13 @@
         </is>
       </c>
       <c r="L143" s="3" t="n">
-        <v>1.82</v>
+        <v>0.48</v>
       </c>
       <c r="M143" s="3" t="n">
-        <v>10.5</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="N143" s="3" t="n">
-        <v>-2.5535</v>
+        <v>-0.9757</v>
       </c>
       <c r="O143" s="3" t="n">
         <v>0</v>
@@ -9787,7 +9787,7 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>ALPA4</t>
+          <t>BRSR6</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -9796,19 +9796,19 @@
         </is>
       </c>
       <c r="C144" s="3" t="n">
-        <v>41.9</v>
+        <v>45.2</v>
       </c>
       <c r="D144" s="3" t="n">
-        <v>15.37</v>
+        <v>18.25</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>12.4</v>
+        <v>14.63</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>-19.32</v>
+        <v>-19.85</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>23.58</v>
+        <v>22.03</v>
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
@@ -9831,13 +9831,13 @@
         </is>
       </c>
       <c r="L144" s="3" t="n">
-        <v>4.06</v>
+        <v>3.53</v>
       </c>
       <c r="M144" s="3" t="n">
-        <v>33.9</v>
+        <v>22.79</v>
       </c>
       <c r="N144" s="3" t="n">
-        <v>-29.4282</v>
+        <v>-9.6351</v>
       </c>
       <c r="O144" s="3" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>TASA4</t>
+          <t>QUAL3</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -9861,19 +9861,19 @@
         </is>
       </c>
       <c r="C145" s="3" t="n">
-        <v>38.7</v>
+        <v>32.3</v>
       </c>
       <c r="D145" s="3" t="n">
-        <v>5.83</v>
+        <v>2.15</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>4.68</v>
+        <v>1.72</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>-19.67</v>
+        <v>-20</v>
       </c>
       <c r="G145" s="3" t="n">
-        <v>5.31</v>
+        <v>9.58</v>
       </c>
       <c r="H145" s="3" t="inlineStr">
         <is>
@@ -9896,13 +9896,13 @@
         </is>
       </c>
       <c r="L145" s="3" t="n">
-        <v>0.48</v>
+        <v>0.7</v>
       </c>
       <c r="M145" s="3" t="n">
-        <v>9.960000000000001</v>
+        <v>37.09</v>
       </c>
       <c r="N145" s="3" t="n">
-        <v>-0.9757</v>
+        <v>-24.6735</v>
       </c>
       <c r="O145" s="3" t="n">
         <v>0</v>
@@ -9917,7 +9917,7 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>BRSR6</t>
+          <t>EMBJ3</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -9926,19 +9926,19 @@
         </is>
       </c>
       <c r="C146" s="3" t="n">
-        <v>45.2</v>
+        <v>46.8</v>
       </c>
       <c r="D146" s="3" t="n">
-        <v>18.25</v>
+        <v>92.41</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>14.63</v>
+        <v>73.38</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>-19.85</v>
+        <v>-20.59</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>22.03</v>
+        <v>12.14</v>
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
@@ -9961,13 +9961,13 @@
         </is>
       </c>
       <c r="L146" s="3" t="n">
-        <v>3.53</v>
+        <v>25.59</v>
       </c>
       <c r="M146" s="3" t="n">
-        <v>22.79</v>
+        <v>33.42</v>
       </c>
       <c r="N146" s="3" t="n">
-        <v>-9.6351</v>
+        <v>-18.971</v>
       </c>
       <c r="O146" s="3" t="n">
         <v>0</v>
@@ -9982,7 +9982,7 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>QUAL3</t>
+          <t>SYNE3</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -9991,19 +9991,19 @@
         </is>
       </c>
       <c r="C147" s="3" t="n">
-        <v>32.3</v>
+        <v>41.9</v>
       </c>
       <c r="D147" s="3" t="n">
-        <v>2.15</v>
+        <v>4.79</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>1.72</v>
+        <v>3.8</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>-20</v>
+        <v>-20.67</v>
       </c>
       <c r="G147" s="3" t="n">
-        <v>9.58</v>
+        <v>6.61</v>
       </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
@@ -10026,13 +10026,13 @@
         </is>
       </c>
       <c r="L147" s="3" t="n">
-        <v>0.7</v>
+        <v>1.01</v>
       </c>
       <c r="M147" s="3" t="n">
-        <v>37.09</v>
+        <v>25.51</v>
       </c>
       <c r="N147" s="3" t="n">
-        <v>-24.6735</v>
+        <v>-7.5717</v>
       </c>
       <c r="O147" s="3" t="n">
         <v>0</v>
@@ -10047,7 +10047,7 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>EMBJ3</t>
+          <t>SAPR3</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -10056,19 +10056,19 @@
         </is>
       </c>
       <c r="C148" s="3" t="n">
-        <v>46.8</v>
+        <v>45.2</v>
       </c>
       <c r="D148" s="3" t="n">
-        <v>92.41</v>
+        <v>10.73</v>
       </c>
       <c r="E148" s="3" t="n">
-        <v>73.38</v>
+        <v>8.5</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>-20.59</v>
+        <v>-20.78</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>12.14</v>
+        <v>15.63</v>
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
@@ -10091,13 +10091,13 @@
         </is>
       </c>
       <c r="L148" s="3" t="n">
-        <v>25.59</v>
+        <v>1.61</v>
       </c>
       <c r="M148" s="3" t="n">
-        <v>33.42</v>
+        <v>17.73</v>
       </c>
       <c r="N148" s="3" t="n">
-        <v>-18.971</v>
+        <v>-6.7081</v>
       </c>
       <c r="O148" s="3" t="n">
         <v>0</v>
@@ -10112,7 +10112,7 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>SYNE3</t>
+          <t>TIMS3</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -10121,19 +10121,19 @@
         </is>
       </c>
       <c r="C149" s="3" t="n">
-        <v>41.9</v>
+        <v>51.6</v>
       </c>
       <c r="D149" s="3" t="n">
-        <v>4.79</v>
+        <v>27.73</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>3.8</v>
+        <v>21.9</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>-20.67</v>
+        <v>-21.03</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>6.61</v>
+        <v>8.26</v>
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
@@ -10156,13 +10156,13 @@
         </is>
       </c>
       <c r="L149" s="3" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="M149" s="3" t="n">
-        <v>25.51</v>
+        <v>8.32</v>
       </c>
       <c r="N149" s="3" t="n">
-        <v>-7.5717</v>
+        <v>-0.7551</v>
       </c>
       <c r="O149" s="3" t="n">
         <v>0</v>
@@ -10177,7 +10177,7 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>SAPR3</t>
+          <t>ROMI3</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -10186,19 +10186,19 @@
         </is>
       </c>
       <c r="C150" s="3" t="n">
-        <v>45.2</v>
+        <v>30.6</v>
       </c>
       <c r="D150" s="3" t="n">
-        <v>10.73</v>
+        <v>8.18</v>
       </c>
       <c r="E150" s="3" t="n">
-        <v>8.5</v>
+        <v>6.45</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>-20.78</v>
+        <v>-21.15</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>15.63</v>
+        <v>4.25</v>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
@@ -10221,13 +10221,13 @@
         </is>
       </c>
       <c r="L150" s="3" t="n">
-        <v>1.61</v>
+        <v>1.32</v>
       </c>
       <c r="M150" s="3" t="n">
-        <v>17.73</v>
+        <v>19.14</v>
       </c>
       <c r="N150" s="3" t="n">
-        <v>-6.7081</v>
+        <v>-6.3597</v>
       </c>
       <c r="O150" s="3" t="n">
         <v>0</v>
@@ -10242,32 +10242,32 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>TIMS3</t>
+          <t>SOJA3</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>Não Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="C151" s="3" t="n">
-        <v>51.6</v>
+        <v>58.1</v>
       </c>
       <c r="D151" s="3" t="n">
-        <v>27.73</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>21.9</v>
+        <v>6.28</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>-21.03</v>
+        <v>-21.79</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>8.26</v>
+        <v>-8.57</v>
       </c>
       <c r="H151" s="3" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="I151" s="3" t="inlineStr">
@@ -10277,7 +10277,7 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="K151" s="3" t="inlineStr">
@@ -10286,13 +10286,13 @@
         </is>
       </c>
       <c r="L151" s="3" t="n">
-        <v>2</v>
+        <v>0.64</v>
       </c>
       <c r="M151" s="3" t="n">
-        <v>8.32</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="N151" s="3" t="n">
-        <v>-0.7551</v>
+        <v>-0.482</v>
       </c>
       <c r="O151" s="3" t="n">
         <v>0</v>
@@ -10307,32 +10307,32 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>ROMI3</t>
+          <t>RAPT4</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>Não Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="C152" s="3" t="n">
-        <v>30.6</v>
+        <v>54.8</v>
       </c>
       <c r="D152" s="3" t="n">
-        <v>8.18</v>
+        <v>6.64</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>6.45</v>
+        <v>5.18</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>-21.15</v>
+        <v>-21.99</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>4.25</v>
+        <v>-2.18</v>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="I152" s="3" t="inlineStr">
@@ -10342,7 +10342,7 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="K152" s="3" t="inlineStr">
@@ -10351,13 +10351,13 @@
         </is>
       </c>
       <c r="L152" s="3" t="n">
-        <v>1.32</v>
+        <v>0.76</v>
       </c>
       <c r="M152" s="3" t="n">
-        <v>19.14</v>
+        <v>14.62</v>
       </c>
       <c r="N152" s="3" t="n">
-        <v>-6.3597</v>
+        <v>-2.4662</v>
       </c>
       <c r="O152" s="3" t="n">
         <v>0</v>
@@ -10372,32 +10372,32 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>SOJA3</t>
+          <t>VULC3</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Não Previsível</t>
         </is>
       </c>
       <c r="C153" s="3" t="n">
-        <v>58.1</v>
+        <v>40.3</v>
       </c>
       <c r="D153" s="3" t="n">
-        <v>8.029999999999999</v>
+        <v>19.03</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>6.28</v>
+        <v>14.82</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>-21.79</v>
+        <v>-22.12</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>-8.57</v>
+        <v>7.62</v>
       </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="I153" s="3" t="inlineStr">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="K153" s="3" t="inlineStr">
@@ -10416,13 +10416,13 @@
         </is>
       </c>
       <c r="L153" s="3" t="n">
-        <v>0.64</v>
+        <v>4.01</v>
       </c>
       <c r="M153" s="3" t="n">
-        <v>9.289999999999999</v>
+        <v>24.96</v>
       </c>
       <c r="N153" s="3" t="n">
-        <v>-0.482</v>
+        <v>-15.6011</v>
       </c>
       <c r="O153" s="3" t="n">
         <v>0</v>
@@ -10437,32 +10437,32 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>RAPT4</t>
+          <t>CSNA3</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Não Previsível</t>
         </is>
       </c>
       <c r="C154" s="3" t="n">
-        <v>54.8</v>
+        <v>43.5</v>
       </c>
       <c r="D154" s="3" t="n">
-        <v>6.64</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="E154" s="3" t="n">
-        <v>5.18</v>
+        <v>6.71</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>-21.99</v>
+        <v>-22.16</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>-2.18</v>
+        <v>10.98</v>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="K154" s="3" t="inlineStr">
@@ -10481,13 +10481,13 @@
         </is>
       </c>
       <c r="L154" s="3" t="n">
-        <v>0.76</v>
+        <v>3.81</v>
       </c>
       <c r="M154" s="3" t="n">
-        <v>14.62</v>
+        <v>58.76</v>
       </c>
       <c r="N154" s="3" t="n">
-        <v>-2.4662</v>
+        <v>-50.3597</v>
       </c>
       <c r="O154" s="3" t="n">
         <v>0</v>
@@ -10502,7 +10502,7 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>VULC3</t>
+          <t>TGMA3</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -10514,16 +10514,16 @@
         <v>40.3</v>
       </c>
       <c r="D155" s="3" t="n">
-        <v>19.03</v>
+        <v>39.45</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>14.82</v>
+        <v>30.65</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>-22.12</v>
+        <v>-22.31</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>7.62</v>
+        <v>7.13</v>
       </c>
       <c r="H155" s="3" t="inlineStr">
         <is>
@@ -10546,13 +10546,13 @@
         </is>
       </c>
       <c r="L155" s="3" t="n">
-        <v>4.01</v>
+        <v>7.82</v>
       </c>
       <c r="M155" s="3" t="n">
-        <v>24.96</v>
+        <v>25.07</v>
       </c>
       <c r="N155" s="3" t="n">
-        <v>-15.6011</v>
+        <v>-7.0851</v>
       </c>
       <c r="O155" s="3" t="n">
         <v>0</v>
@@ -10567,32 +10567,32 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>CSNA3</t>
+          <t>MBRF3</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>Não Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="C156" s="3" t="n">
-        <v>43.5</v>
+        <v>58.1</v>
       </c>
       <c r="D156" s="3" t="n">
-        <v>8.619999999999999</v>
+        <v>20.68</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>6.71</v>
+        <v>16.01</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>-22.16</v>
+        <v>-22.58</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>10.98</v>
+        <v>-9.23</v>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="I156" s="3" t="inlineStr">
@@ -10602,7 +10602,7 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="K156" s="3" t="inlineStr">
@@ -10611,13 +10611,13 @@
         </is>
       </c>
       <c r="L156" s="3" t="n">
-        <v>3.81</v>
+        <v>1.41</v>
       </c>
       <c r="M156" s="3" t="n">
-        <v>58.76</v>
+        <v>7.23</v>
       </c>
       <c r="N156" s="3" t="n">
-        <v>-50.3597</v>
+        <v>-0.2264</v>
       </c>
       <c r="O156" s="3" t="n">
         <v>0</v>
@@ -10632,7 +10632,7 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>TGMA3</t>
+          <t>DASA3</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -10641,19 +10641,19 @@
         </is>
       </c>
       <c r="C157" s="3" t="n">
-        <v>40.3</v>
+        <v>46.8</v>
       </c>
       <c r="D157" s="3" t="n">
-        <v>39.45</v>
+        <v>4.03</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>30.65</v>
+        <v>3.1</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>-22.31</v>
+        <v>-23.08</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>7.13</v>
+        <v>37.26</v>
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
@@ -10676,13 +10676,13 @@
         </is>
       </c>
       <c r="L157" s="3" t="n">
-        <v>7.82</v>
+        <v>2.11</v>
       </c>
       <c r="M157" s="3" t="n">
-        <v>25.07</v>
+        <v>65.39</v>
       </c>
       <c r="N157" s="3" t="n">
-        <v>-7.0851</v>
+        <v>-62.8458</v>
       </c>
       <c r="O157" s="3" t="n">
         <v>0</v>
@@ -10697,32 +10697,32 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>MBRF3</t>
+          <t>HBSA3</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Não Previsível</t>
         </is>
       </c>
       <c r="C158" s="3" t="n">
-        <v>58.1</v>
+        <v>40.3</v>
       </c>
       <c r="D158" s="3" t="n">
-        <v>20.68</v>
+        <v>4.2</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>16.01</v>
+        <v>3.23</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>-22.58</v>
+        <v>-23.1</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>-9.23</v>
+        <v>5.9</v>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="I158" s="3" t="inlineStr">
@@ -10732,7 +10732,7 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="K158" s="3" t="inlineStr">
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="L158" s="3" t="n">
-        <v>1.41</v>
+        <v>0.51</v>
       </c>
       <c r="M158" s="3" t="n">
-        <v>7.23</v>
+        <v>14.91</v>
       </c>
       <c r="N158" s="3" t="n">
-        <v>-0.2264</v>
+        <v>-2.2937</v>
       </c>
       <c r="O158" s="3" t="n">
         <v>0</v>
@@ -10762,7 +10762,7 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>DASA3</t>
+          <t>JSLG3</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -10774,16 +10774,16 @@
         <v>46.8</v>
       </c>
       <c r="D159" s="3" t="n">
-        <v>4.03</v>
+        <v>8.25</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>3.1</v>
+        <v>6.28</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>-23.08</v>
+        <v>-23.88</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>37.26</v>
+        <v>23.9</v>
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
@@ -10806,13 +10806,13 @@
         </is>
       </c>
       <c r="L159" s="3" t="n">
-        <v>2.11</v>
+        <v>1.13</v>
       </c>
       <c r="M159" s="3" t="n">
-        <v>65.39</v>
+        <v>16.64</v>
       </c>
       <c r="N159" s="3" t="n">
-        <v>-62.8458</v>
+        <v>-2.5426</v>
       </c>
       <c r="O159" s="3" t="n">
         <v>0</v>
@@ -10827,7 +10827,7 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>HBSA3</t>
+          <t>BBAS3</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -10836,19 +10836,19 @@
         </is>
       </c>
       <c r="C160" s="3" t="n">
-        <v>40.3</v>
+        <v>41.9</v>
       </c>
       <c r="D160" s="3" t="n">
-        <v>4.2</v>
+        <v>26.88</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>3.23</v>
+        <v>20.3</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>-23.1</v>
+        <v>-24.48</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>5.9</v>
+        <v>9.08</v>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
@@ -10871,13 +10871,13 @@
         </is>
       </c>
       <c r="L160" s="3" t="n">
-        <v>0.51</v>
+        <v>2.66</v>
       </c>
       <c r="M160" s="3" t="n">
-        <v>14.91</v>
+        <v>12.1</v>
       </c>
       <c r="N160" s="3" t="n">
-        <v>-2.2937</v>
+        <v>-2.7379</v>
       </c>
       <c r="O160" s="3" t="n">
         <v>0</v>
@@ -10892,7 +10892,7 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>JSLG3</t>
+          <t>RADL3</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -10901,19 +10901,19 @@
         </is>
       </c>
       <c r="C161" s="3" t="n">
-        <v>46.8</v>
+        <v>37.1</v>
       </c>
       <c r="D161" s="3" t="n">
-        <v>8.25</v>
+        <v>24.98</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>6.28</v>
+        <v>18.69</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>-23.88</v>
+        <v>-25.18</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>23.9</v>
+        <v>19.15</v>
       </c>
       <c r="H161" s="3" t="inlineStr">
         <is>
@@ -10936,13 +10936,13 @@
         </is>
       </c>
       <c r="L161" s="3" t="n">
-        <v>1.13</v>
+        <v>7.28</v>
       </c>
       <c r="M161" s="3" t="n">
-        <v>16.64</v>
+        <v>34.56</v>
       </c>
       <c r="N161" s="3" t="n">
-        <v>-2.5426</v>
+        <v>-16.3928</v>
       </c>
       <c r="O161" s="3" t="n">
         <v>0</v>
@@ -10957,7 +10957,7 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>BBAS3</t>
+          <t>ESPA3</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -10966,23 +10966,23 @@
         </is>
       </c>
       <c r="C162" s="3" t="n">
-        <v>41.9</v>
+        <v>46.8</v>
       </c>
       <c r="D162" s="3" t="n">
-        <v>26.88</v>
+        <v>1.07</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>20.3</v>
+        <v>0.8</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>-24.48</v>
+        <v>-25.19</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>9.08</v>
+        <v>-6.38</v>
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="I162" s="3" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="K162" s="3" t="inlineStr">
@@ -11001,13 +11001,13 @@
         </is>
       </c>
       <c r="L162" s="3" t="n">
-        <v>2.66</v>
+        <v>0.17</v>
       </c>
       <c r="M162" s="3" t="n">
-        <v>12.1</v>
+        <v>15.08</v>
       </c>
       <c r="N162" s="3" t="n">
-        <v>-2.7379</v>
+        <v>-0.5779</v>
       </c>
       <c r="O162" s="3" t="n">
         <v>0</v>
@@ -11022,32 +11022,32 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>RADL3</t>
+          <t>GMAT3</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>Não Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="C163" s="3" t="n">
-        <v>37.1</v>
+        <v>54.8</v>
       </c>
       <c r="D163" s="3" t="n">
-        <v>24.98</v>
+        <v>5.72</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>18.69</v>
+        <v>4.27</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>-25.18</v>
+        <v>-25.35</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>19.15</v>
+        <v>-28.18</v>
       </c>
       <c r="H163" s="3" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="I163" s="3" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="K163" s="3" t="inlineStr">
@@ -11066,13 +11066,13 @@
         </is>
       </c>
       <c r="L163" s="3" t="n">
-        <v>7.28</v>
+        <v>0.85</v>
       </c>
       <c r="M163" s="3" t="n">
-        <v>34.56</v>
+        <v>18.32</v>
       </c>
       <c r="N163" s="3" t="n">
-        <v>-16.3928</v>
+        <v>-4.5333</v>
       </c>
       <c r="O163" s="3" t="n">
         <v>0</v>
@@ -11087,7 +11087,7 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>ESPA3</t>
+          <t>PNVL3</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -11096,23 +11096,23 @@
         </is>
       </c>
       <c r="C164" s="3" t="n">
-        <v>46.8</v>
+        <v>40.3</v>
       </c>
       <c r="D164" s="3" t="n">
-        <v>1.07</v>
+        <v>16.1</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>0.8</v>
+        <v>11.9</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>-25.19</v>
+        <v>-26.1</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>-6.38</v>
+        <v>16.92</v>
       </c>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="I164" s="3" t="inlineStr">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="K164" s="3" t="inlineStr">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L164" s="3" t="n">
-        <v>0.17</v>
+        <v>1.42</v>
       </c>
       <c r="M164" s="3" t="n">
-        <v>15.08</v>
+        <v>10.89</v>
       </c>
       <c r="N164" s="3" t="n">
-        <v>-0.5779</v>
+        <v>-1.629</v>
       </c>
       <c r="O164" s="3" t="n">
         <v>0</v>
@@ -11152,7 +11152,7 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>GMAT3</t>
+          <t>AZZA3</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -11164,16 +11164,16 @@
         <v>54.8</v>
       </c>
       <c r="D165" s="3" t="n">
-        <v>5.72</v>
+        <v>26.17</v>
       </c>
       <c r="E165" s="3" t="n">
-        <v>4.27</v>
+        <v>19.31</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>-25.35</v>
+        <v>-26.21</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>-28.18</v>
+        <v>-12.56</v>
       </c>
       <c r="H165" s="3" t="inlineStr">
         <is>
@@ -11196,13 +11196,13 @@
         </is>
       </c>
       <c r="L165" s="3" t="n">
-        <v>0.85</v>
+        <v>1.95</v>
       </c>
       <c r="M165" s="3" t="n">
-        <v>18.32</v>
+        <v>7.9</v>
       </c>
       <c r="N165" s="3" t="n">
-        <v>-4.5333</v>
+        <v>0.214</v>
       </c>
       <c r="O165" s="3" t="n">
         <v>0</v>
@@ -11217,7 +11217,7 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>PNVL3</t>
+          <t>CYRE3</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -11226,19 +11226,19 @@
         </is>
       </c>
       <c r="C166" s="3" t="n">
-        <v>40.3</v>
+        <v>38.7</v>
       </c>
       <c r="D166" s="3" t="n">
-        <v>16.1</v>
+        <v>30.71</v>
       </c>
       <c r="E166" s="3" t="n">
-        <v>11.9</v>
+        <v>22.52</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>-26.1</v>
+        <v>-26.67</v>
       </c>
       <c r="G166" s="3" t="n">
-        <v>16.92</v>
+        <v>9.24</v>
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
@@ -11261,13 +11261,13 @@
         </is>
       </c>
       <c r="L166" s="3" t="n">
-        <v>1.42</v>
+        <v>7.3</v>
       </c>
       <c r="M166" s="3" t="n">
-        <v>10.89</v>
+        <v>30.23</v>
       </c>
       <c r="N166" s="3" t="n">
-        <v>-1.629</v>
+        <v>-7.9377</v>
       </c>
       <c r="O166" s="3" t="n">
         <v>0</v>
@@ -11282,32 +11282,32 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>AZZA3</t>
+          <t>ECOR3</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Não Previsível</t>
         </is>
       </c>
       <c r="C167" s="3" t="n">
-        <v>54.8</v>
+        <v>41.9</v>
       </c>
       <c r="D167" s="3" t="n">
-        <v>26.17</v>
+        <v>10.32</v>
       </c>
       <c r="E167" s="3" t="n">
-        <v>19.31</v>
+        <v>7.53</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>-26.21</v>
+        <v>-27.06</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>-12.56</v>
+        <v>18.81</v>
       </c>
       <c r="H167" s="3" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="I167" s="3" t="inlineStr">
@@ -11317,7 +11317,7 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="K167" s="3" t="inlineStr">
@@ -11326,13 +11326,13 @@
         </is>
       </c>
       <c r="L167" s="3" t="n">
-        <v>1.95</v>
+        <v>3.71</v>
       </c>
       <c r="M167" s="3" t="n">
-        <v>7.9</v>
+        <v>44.47</v>
       </c>
       <c r="N167" s="3" t="n">
-        <v>0.214</v>
+        <v>-24.6229</v>
       </c>
       <c r="O167" s="3" t="n">
         <v>0</v>
@@ -11347,7 +11347,7 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>CYRE3</t>
+          <t>FESA4</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -11356,19 +11356,19 @@
         </is>
       </c>
       <c r="C168" s="3" t="n">
-        <v>38.7</v>
+        <v>40.3</v>
       </c>
       <c r="D168" s="3" t="n">
-        <v>30.71</v>
+        <v>8.48</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>22.52</v>
+        <v>6.18</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>-26.67</v>
+        <v>-27.12</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>9.24</v>
+        <v>13.17</v>
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
@@ -11391,13 +11391,13 @@
         </is>
       </c>
       <c r="L168" s="3" t="n">
-        <v>7.3</v>
+        <v>0.99</v>
       </c>
       <c r="M168" s="3" t="n">
-        <v>30.23</v>
+        <v>14.68</v>
       </c>
       <c r="N168" s="3" t="n">
-        <v>-7.9377</v>
+        <v>-2.3536</v>
       </c>
       <c r="O168" s="3" t="n">
         <v>0</v>
@@ -11412,7 +11412,7 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>ECOR3</t>
+          <t>KEPL3</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -11424,16 +11424,16 @@
         <v>41.9</v>
       </c>
       <c r="D169" s="3" t="n">
-        <v>10.32</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="E169" s="3" t="n">
-        <v>7.53</v>
+        <v>7.04</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>-27.06</v>
+        <v>-27.5</v>
       </c>
       <c r="G169" s="3" t="n">
-        <v>18.81</v>
+        <v>16.33</v>
       </c>
       <c r="H169" s="3" t="inlineStr">
         <is>
@@ -11456,13 +11456,13 @@
         </is>
       </c>
       <c r="L169" s="3" t="n">
-        <v>3.71</v>
+        <v>3.58</v>
       </c>
       <c r="M169" s="3" t="n">
-        <v>44.47</v>
+        <v>46.31</v>
       </c>
       <c r="N169" s="3" t="n">
-        <v>-24.6229</v>
+        <v>-43.4883</v>
       </c>
       <c r="O169" s="3" t="n">
         <v>0</v>
@@ -11477,7 +11477,7 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>FESA4</t>
+          <t>SUZB3</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -11486,19 +11486,19 @@
         </is>
       </c>
       <c r="C170" s="3" t="n">
-        <v>40.3</v>
+        <v>37.1</v>
       </c>
       <c r="D170" s="3" t="n">
-        <v>8.48</v>
+        <v>57.99</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>6.18</v>
+        <v>41.91</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>-27.12</v>
+        <v>-27.73</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>13.17</v>
+        <v>2.08</v>
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
@@ -11521,13 +11521,13 @@
         </is>
       </c>
       <c r="L170" s="3" t="n">
-        <v>0.99</v>
+        <v>5.55</v>
       </c>
       <c r="M170" s="3" t="n">
-        <v>14.68</v>
+        <v>12.31</v>
       </c>
       <c r="N170" s="3" t="n">
-        <v>-2.3536</v>
+        <v>-0.7494</v>
       </c>
       <c r="O170" s="3" t="n">
         <v>0</v>
@@ -11542,7 +11542,7 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>KEPL3</t>
+          <t>YDUQ3</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -11551,19 +11551,19 @@
         </is>
       </c>
       <c r="C171" s="3" t="n">
-        <v>41.9</v>
+        <v>43.5</v>
       </c>
       <c r="D171" s="3" t="n">
-        <v>9.710000000000001</v>
+        <v>13.27</v>
       </c>
       <c r="E171" s="3" t="n">
-        <v>7.04</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>-27.5</v>
+        <v>-28.11</v>
       </c>
       <c r="G171" s="3" t="n">
-        <v>16.33</v>
+        <v>2.73</v>
       </c>
       <c r="H171" s="3" t="inlineStr">
         <is>
@@ -11586,13 +11586,13 @@
         </is>
       </c>
       <c r="L171" s="3" t="n">
-        <v>3.58</v>
+        <v>2.37</v>
       </c>
       <c r="M171" s="3" t="n">
-        <v>46.31</v>
+        <v>22.91</v>
       </c>
       <c r="N171" s="3" t="n">
-        <v>-43.4883</v>
+        <v>-5.5518</v>
       </c>
       <c r="O171" s="3" t="n">
         <v>0</v>
@@ -11607,7 +11607,7 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>SUZB3</t>
+          <t>COGN3</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -11616,19 +11616,19 @@
         </is>
       </c>
       <c r="C172" s="3" t="n">
-        <v>37.1</v>
+        <v>40.3</v>
       </c>
       <c r="D172" s="3" t="n">
-        <v>57.99</v>
+        <v>3.48</v>
       </c>
       <c r="E172" s="3" t="n">
-        <v>41.91</v>
+        <v>2.5</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>-27.73</v>
+        <v>-28.22</v>
       </c>
       <c r="G172" s="3" t="n">
-        <v>2.08</v>
+        <v>17.61</v>
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
@@ -11651,13 +11651,13 @@
         </is>
       </c>
       <c r="L172" s="3" t="n">
-        <v>5.55</v>
+        <v>1.36</v>
       </c>
       <c r="M172" s="3" t="n">
-        <v>12.31</v>
+        <v>48.21</v>
       </c>
       <c r="N172" s="3" t="n">
-        <v>-0.7494</v>
+        <v>-25.7356</v>
       </c>
       <c r="O172" s="3" t="n">
         <v>0</v>
@@ -11672,7 +11672,7 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>YDUQ3</t>
+          <t>BEEF3</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -11681,19 +11681,19 @@
         </is>
       </c>
       <c r="C173" s="3" t="n">
-        <v>43.5</v>
+        <v>38.7</v>
       </c>
       <c r="D173" s="3" t="n">
-        <v>13.27</v>
+        <v>5.18</v>
       </c>
       <c r="E173" s="3" t="n">
-        <v>9.539999999999999</v>
+        <v>3.69</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>-28.11</v>
+        <v>-28.75</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>2.73</v>
+        <v>1.86</v>
       </c>
       <c r="H173" s="3" t="inlineStr">
         <is>
@@ -11716,13 +11716,13 @@
         </is>
       </c>
       <c r="L173" s="3" t="n">
-        <v>2.37</v>
+        <v>1.9</v>
       </c>
       <c r="M173" s="3" t="n">
-        <v>22.91</v>
+        <v>46.21</v>
       </c>
       <c r="N173" s="3" t="n">
-        <v>-5.5518</v>
+        <v>-44.3482</v>
       </c>
       <c r="O173" s="3" t="n">
         <v>0</v>
@@ -11737,7 +11737,7 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>COGN3</t>
+          <t>AMAR3</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -11746,23 +11746,23 @@
         </is>
       </c>
       <c r="C174" s="3" t="n">
-        <v>40.3</v>
+        <v>46.8</v>
       </c>
       <c r="D174" s="3" t="n">
-        <v>3.48</v>
+        <v>0.9</v>
       </c>
       <c r="E174" s="3" t="n">
-        <v>2.5</v>
+        <v>0.64</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>-28.22</v>
+        <v>-28.89</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>17.61</v>
+        <v>-17.23</v>
       </c>
       <c r="H174" s="3" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="I174" s="3" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="K174" s="3" t="inlineStr">
@@ -11781,13 +11781,13 @@
         </is>
       </c>
       <c r="L174" s="3" t="n">
-        <v>1.36</v>
+        <v>0.04</v>
       </c>
       <c r="M174" s="3" t="n">
-        <v>48.21</v>
+        <v>5.5</v>
       </c>
       <c r="N174" s="3" t="n">
-        <v>-25.7356</v>
+        <v>0.5167</v>
       </c>
       <c r="O174" s="3" t="n">
         <v>0</v>
@@ -11802,7 +11802,7 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>BEEF3</t>
+          <t>SIMH3</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -11811,19 +11811,19 @@
         </is>
       </c>
       <c r="C175" s="3" t="n">
-        <v>38.7</v>
+        <v>37.1</v>
       </c>
       <c r="D175" s="3" t="n">
-        <v>5.18</v>
+        <v>12.65</v>
       </c>
       <c r="E175" s="3" t="n">
-        <v>3.69</v>
+        <v>8.92</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>-28.75</v>
+        <v>-29.49</v>
       </c>
       <c r="G175" s="3" t="n">
-        <v>1.86</v>
+        <v>13.24</v>
       </c>
       <c r="H175" s="3" t="inlineStr">
         <is>
@@ -11846,13 +11846,13 @@
         </is>
       </c>
       <c r="L175" s="3" t="n">
-        <v>1.9</v>
+        <v>2.84</v>
       </c>
       <c r="M175" s="3" t="n">
-        <v>46.21</v>
+        <v>27.56</v>
       </c>
       <c r="N175" s="3" t="n">
-        <v>-44.3482</v>
+        <v>-8.755599999999999</v>
       </c>
       <c r="O175" s="3" t="n">
         <v>0</v>
@@ -11867,7 +11867,7 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>AMAR3</t>
+          <t>VIVA3</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -11876,23 +11876,23 @@
         </is>
       </c>
       <c r="C176" s="3" t="n">
-        <v>46.8</v>
+        <v>33.9</v>
       </c>
       <c r="D176" s="3" t="n">
-        <v>0.9</v>
+        <v>31.15</v>
       </c>
       <c r="E176" s="3" t="n">
-        <v>0.64</v>
+        <v>21.84</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>-28.89</v>
+        <v>-29.89</v>
       </c>
       <c r="G176" s="3" t="n">
-        <v>-17.23</v>
+        <v>6.4</v>
       </c>
       <c r="H176" s="3" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="I176" s="3" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="K176" s="3" t="inlineStr">
@@ -11911,13 +11911,13 @@
         </is>
       </c>
       <c r="L176" s="3" t="n">
-        <v>0.04</v>
+        <v>6.94</v>
       </c>
       <c r="M176" s="3" t="n">
-        <v>5.5</v>
+        <v>28</v>
       </c>
       <c r="N176" s="3" t="n">
-        <v>0.5167</v>
+        <v>-8.5067</v>
       </c>
       <c r="O176" s="3" t="n">
         <v>0</v>
@@ -11932,7 +11932,7 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>SIMH3</t>
+          <t>VAMO3</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -11941,19 +11941,19 @@
         </is>
       </c>
       <c r="C177" s="3" t="n">
-        <v>37.1</v>
+        <v>40.3</v>
       </c>
       <c r="D177" s="3" t="n">
-        <v>12.65</v>
+        <v>4.4</v>
       </c>
       <c r="E177" s="3" t="n">
-        <v>8.92</v>
+        <v>3.06</v>
       </c>
       <c r="F177" s="3" t="n">
-        <v>-29.49</v>
+        <v>-30.45</v>
       </c>
       <c r="G177" s="3" t="n">
-        <v>13.24</v>
+        <v>4.66</v>
       </c>
       <c r="H177" s="3" t="inlineStr">
         <is>
@@ -11976,13 +11976,13 @@
         </is>
       </c>
       <c r="L177" s="3" t="n">
-        <v>2.84</v>
+        <v>0.35</v>
       </c>
       <c r="M177" s="3" t="n">
-        <v>27.56</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="N177" s="3" t="n">
-        <v>-8.755599999999999</v>
+        <v>-0.2882</v>
       </c>
       <c r="O177" s="3" t="n">
         <v>0</v>
@@ -11997,7 +11997,7 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>VIVA3</t>
+          <t>EVEN3</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -12006,19 +12006,19 @@
         </is>
       </c>
       <c r="C178" s="3" t="n">
-        <v>33.9</v>
+        <v>45.2</v>
       </c>
       <c r="D178" s="3" t="n">
-        <v>31.15</v>
+        <v>8.35</v>
       </c>
       <c r="E178" s="3" t="n">
-        <v>21.84</v>
+        <v>5.77</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>-29.89</v>
+        <v>-30.9</v>
       </c>
       <c r="G178" s="3" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="H178" s="3" t="inlineStr">
         <is>
@@ -12041,13 +12041,13 @@
         </is>
       </c>
       <c r="L178" s="3" t="n">
-        <v>6.94</v>
+        <v>1.88</v>
       </c>
       <c r="M178" s="3" t="n">
-        <v>28</v>
+        <v>29.89</v>
       </c>
       <c r="N178" s="3" t="n">
-        <v>-8.5067</v>
+        <v>-7.2891</v>
       </c>
       <c r="O178" s="3" t="n">
         <v>0</v>
@@ -12062,7 +12062,7 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>VAMO3</t>
+          <t>GGPS3</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -12071,19 +12071,19 @@
         </is>
       </c>
       <c r="C179" s="3" t="n">
-        <v>40.3</v>
+        <v>27.4</v>
       </c>
       <c r="D179" s="3" t="n">
-        <v>4.4</v>
+        <v>18.41</v>
       </c>
       <c r="E179" s="3" t="n">
-        <v>3.06</v>
+        <v>12.21</v>
       </c>
       <c r="F179" s="3" t="n">
-        <v>-30.45</v>
+        <v>-33.68</v>
       </c>
       <c r="G179" s="3" t="n">
-        <v>4.66</v>
+        <v>10.49</v>
       </c>
       <c r="H179" s="3" t="inlineStr">
         <is>
@@ -12106,13 +12106,13 @@
         </is>
       </c>
       <c r="L179" s="3" t="n">
-        <v>0.35</v>
+        <v>4.12</v>
       </c>
       <c r="M179" s="3" t="n">
-        <v>9.640000000000001</v>
+        <v>28.18</v>
       </c>
       <c r="N179" s="3" t="n">
-        <v>-0.2882</v>
+        <v>-6.9848</v>
       </c>
       <c r="O179" s="3" t="n">
         <v>0</v>
@@ -12127,32 +12127,32 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>EVEN3</t>
+          <t>AALR3</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>Não Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="C180" s="3" t="n">
-        <v>45.2</v>
+        <v>53.2</v>
       </c>
       <c r="D180" s="3" t="n">
-        <v>8.35</v>
+        <v>5.4</v>
       </c>
       <c r="E180" s="3" t="n">
-        <v>5.77</v>
+        <v>3.55</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>-30.9</v>
+        <v>-34.26</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>9</v>
+        <v>-18.25</v>
       </c>
       <c r="H180" s="3" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="I180" s="3" t="inlineStr">
@@ -12162,7 +12162,7 @@
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="K180" s="3" t="inlineStr">
@@ -12171,13 +12171,13 @@
         </is>
       </c>
       <c r="L180" s="3" t="n">
-        <v>1.88</v>
+        <v>0.39</v>
       </c>
       <c r="M180" s="3" t="n">
-        <v>29.89</v>
+        <v>11.46</v>
       </c>
       <c r="N180" s="3" t="n">
-        <v>-7.2891</v>
+        <v>0.3416</v>
       </c>
       <c r="O180" s="3" t="n">
         <v>0</v>
@@ -12192,7 +12192,7 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>AMBP3</t>
+          <t>LJQQ3</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -12201,23 +12201,23 @@
         </is>
       </c>
       <c r="C181" s="3" t="n">
-        <v>35.5</v>
+        <v>51.6</v>
       </c>
       <c r="D181" s="3" t="n">
-        <v>0.25</v>
+        <v>2.15</v>
       </c>
       <c r="E181" s="3" t="n">
-        <v>0.17</v>
+        <v>1.41</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>-32</v>
+        <v>-34.42</v>
       </c>
       <c r="G181" s="3" t="n">
-        <v>172.27</v>
+        <v>-1.84</v>
       </c>
       <c r="H181" s="3" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="I181" s="3" t="inlineStr">
@@ -12227,7 +12227,7 @@
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="K181" s="3" t="inlineStr">
@@ -12236,13 +12236,13 @@
         </is>
       </c>
       <c r="L181" s="3" t="n">
-        <v>8.15</v>
+        <v>0.39</v>
       </c>
       <c r="M181" s="3" t="n">
-        <v>3939.81</v>
+        <v>23.55</v>
       </c>
       <c r="N181" s="3" t="n">
-        <v>-137320.0493</v>
+        <v>-2.055</v>
       </c>
       <c r="O181" s="3" t="n">
         <v>0</v>
@@ -12257,7 +12257,7 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>GGPS3</t>
+          <t>ANIM3</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -12266,19 +12266,19 @@
         </is>
       </c>
       <c r="C182" s="3" t="n">
-        <v>27.4</v>
+        <v>35.5</v>
       </c>
       <c r="D182" s="3" t="n">
-        <v>18.41</v>
+        <v>5.03</v>
       </c>
       <c r="E182" s="3" t="n">
-        <v>12.21</v>
+        <v>3.3</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>-33.68</v>
+        <v>-34.44</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>10.49</v>
+        <v>13.6</v>
       </c>
       <c r="H182" s="3" t="inlineStr">
         <is>
@@ -12301,13 +12301,13 @@
         </is>
       </c>
       <c r="L182" s="3" t="n">
-        <v>4.12</v>
+        <v>0.72</v>
       </c>
       <c r="M182" s="3" t="n">
-        <v>28.18</v>
+        <v>19.57</v>
       </c>
       <c r="N182" s="3" t="n">
-        <v>-6.9848</v>
+        <v>-3.0874</v>
       </c>
       <c r="O182" s="3" t="n">
         <v>0</v>
@@ -12322,32 +12322,32 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>AALR3</t>
+          <t>CVCB3</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Não Previsível</t>
         </is>
       </c>
       <c r="C183" s="3" t="n">
-        <v>53.2</v>
+        <v>29</v>
       </c>
       <c r="D183" s="3" t="n">
-        <v>5.4</v>
+        <v>2.3</v>
       </c>
       <c r="E183" s="3" t="n">
-        <v>3.55</v>
+        <v>1.5</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>-34.26</v>
+        <v>-34.78</v>
       </c>
       <c r="G183" s="3" t="n">
-        <v>-18.25</v>
+        <v>6.75</v>
       </c>
       <c r="H183" s="3" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="I183" s="3" t="inlineStr">
@@ -12357,7 +12357,7 @@
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="K183" s="3" t="inlineStr">
@@ -12366,13 +12366,13 @@
         </is>
       </c>
       <c r="L183" s="3" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="M183" s="3" t="n">
-        <v>11.46</v>
+        <v>19.46</v>
       </c>
       <c r="N183" s="3" t="n">
-        <v>0.3416</v>
+        <v>-3.8815</v>
       </c>
       <c r="O183" s="3" t="n">
         <v>0</v>
@@ -12387,7 +12387,7 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>LJQQ3</t>
+          <t>MGLU3</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -12396,23 +12396,23 @@
         </is>
       </c>
       <c r="C184" s="3" t="n">
-        <v>51.6</v>
+        <v>40.3</v>
       </c>
       <c r="D184" s="3" t="n">
-        <v>2.15</v>
+        <v>9.26</v>
       </c>
       <c r="E184" s="3" t="n">
-        <v>1.41</v>
+        <v>5.98</v>
       </c>
       <c r="F184" s="3" t="n">
-        <v>-34.42</v>
+        <v>-35.44</v>
       </c>
       <c r="G184" s="3" t="n">
-        <v>-1.84</v>
+        <v>11.39</v>
       </c>
       <c r="H184" s="3" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="I184" s="3" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="K184" s="3" t="inlineStr">
@@ -12431,13 +12431,13 @@
         </is>
       </c>
       <c r="L184" s="3" t="n">
-        <v>0.39</v>
+        <v>2.31</v>
       </c>
       <c r="M184" s="3" t="n">
-        <v>23.55</v>
+        <v>30.5</v>
       </c>
       <c r="N184" s="3" t="n">
-        <v>-2.055</v>
+        <v>-5.6504</v>
       </c>
       <c r="O184" s="3" t="n">
         <v>0</v>
@@ -12452,7 +12452,7 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>ANIM3</t>
+          <t>MOVI3</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -12461,19 +12461,19 @@
         </is>
       </c>
       <c r="C185" s="3" t="n">
-        <v>35.5</v>
+        <v>41.9</v>
       </c>
       <c r="D185" s="3" t="n">
-        <v>5.03</v>
+        <v>14.81</v>
       </c>
       <c r="E185" s="3" t="n">
-        <v>3.3</v>
+        <v>9.51</v>
       </c>
       <c r="F185" s="3" t="n">
-        <v>-34.44</v>
+        <v>-35.79</v>
       </c>
       <c r="G185" s="3" t="n">
-        <v>13.6</v>
+        <v>24.08</v>
       </c>
       <c r="H185" s="3" t="inlineStr">
         <is>
@@ -12496,13 +12496,13 @@
         </is>
       </c>
       <c r="L185" s="3" t="n">
-        <v>0.72</v>
+        <v>2.46</v>
       </c>
       <c r="M185" s="3" t="n">
-        <v>19.57</v>
+        <v>22.75</v>
       </c>
       <c r="N185" s="3" t="n">
-        <v>-3.0874</v>
+        <v>-3.594</v>
       </c>
       <c r="O185" s="3" t="n">
         <v>0</v>
@@ -12517,7 +12517,7 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>CVCB3</t>
+          <t>LAVV3</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -12526,19 +12526,19 @@
         </is>
       </c>
       <c r="C186" s="3" t="n">
-        <v>29</v>
+        <v>40.3</v>
       </c>
       <c r="D186" s="3" t="n">
-        <v>2.3</v>
+        <v>18.41</v>
       </c>
       <c r="E186" s="3" t="n">
-        <v>1.5</v>
+        <v>11.72</v>
       </c>
       <c r="F186" s="3" t="n">
-        <v>-34.78</v>
+        <v>-36.34</v>
       </c>
       <c r="G186" s="3" t="n">
-        <v>6.75</v>
+        <v>18.37</v>
       </c>
       <c r="H186" s="3" t="inlineStr">
         <is>
@@ -12561,13 +12561,13 @@
         </is>
       </c>
       <c r="L186" s="3" t="n">
-        <v>0.37</v>
+        <v>5.26</v>
       </c>
       <c r="M186" s="3" t="n">
-        <v>19.46</v>
+        <v>40.74</v>
       </c>
       <c r="N186" s="3" t="n">
-        <v>-3.8815</v>
+        <v>-7.8498</v>
       </c>
       <c r="O186" s="3" t="n">
         <v>0</v>
@@ -12582,7 +12582,7 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>MGLU3</t>
+          <t>OIBR3</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -12591,23 +12591,23 @@
         </is>
       </c>
       <c r="C187" s="3" t="n">
-        <v>40.3</v>
+        <v>27.4</v>
       </c>
       <c r="D187" s="3" t="n">
-        <v>9.26</v>
+        <v>0.19</v>
       </c>
       <c r="E187" s="3" t="n">
-        <v>5.98</v>
+        <v>0.12</v>
       </c>
       <c r="F187" s="3" t="n">
-        <v>-35.44</v>
+        <v>-36.84</v>
       </c>
       <c r="G187" s="3" t="n">
-        <v>11.39</v>
+        <v>-364.44</v>
       </c>
       <c r="H187" s="3" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="I187" s="3" t="inlineStr">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="K187" s="3" t="inlineStr">
@@ -12626,13 +12626,13 @@
         </is>
       </c>
       <c r="L187" s="3" t="n">
-        <v>2.31</v>
+        <v>0.2</v>
       </c>
       <c r="M187" s="3" t="n">
-        <v>30.5</v>
+        <v>139.02</v>
       </c>
       <c r="N187" s="3" t="n">
-        <v>-5.6504</v>
+        <v>-89.8707</v>
       </c>
       <c r="O187" s="3" t="n">
         <v>0</v>
@@ -12647,7 +12647,7 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>MOVI3</t>
+          <t>ARML3</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -12656,19 +12656,19 @@
         </is>
       </c>
       <c r="C188" s="3" t="n">
-        <v>41.9</v>
+        <v>40.3</v>
       </c>
       <c r="D188" s="3" t="n">
-        <v>14.81</v>
+        <v>5.9</v>
       </c>
       <c r="E188" s="3" t="n">
-        <v>9.51</v>
+        <v>3.65</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>-35.79</v>
+        <v>-38.14</v>
       </c>
       <c r="G188" s="3" t="n">
-        <v>24.08</v>
+        <v>17.68</v>
       </c>
       <c r="H188" s="3" t="inlineStr">
         <is>
@@ -12691,13 +12691,13 @@
         </is>
       </c>
       <c r="L188" s="3" t="n">
-        <v>2.46</v>
+        <v>0.76</v>
       </c>
       <c r="M188" s="3" t="n">
-        <v>22.75</v>
+        <v>18.97</v>
       </c>
       <c r="N188" s="3" t="n">
-        <v>-3.594</v>
+        <v>-1.038</v>
       </c>
       <c r="O188" s="3" t="n">
         <v>0</v>
@@ -12712,7 +12712,7 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>LAVV3</t>
+          <t>PGMN3</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -12721,19 +12721,19 @@
         </is>
       </c>
       <c r="C189" s="3" t="n">
-        <v>40.3</v>
+        <v>38.7</v>
       </c>
       <c r="D189" s="3" t="n">
-        <v>18.41</v>
+        <v>6.97</v>
       </c>
       <c r="E189" s="3" t="n">
-        <v>11.72</v>
+        <v>4.27</v>
       </c>
       <c r="F189" s="3" t="n">
-        <v>-36.34</v>
+        <v>-38.74</v>
       </c>
       <c r="G189" s="3" t="n">
-        <v>18.37</v>
+        <v>26.56</v>
       </c>
       <c r="H189" s="3" t="inlineStr">
         <is>
@@ -12756,13 +12756,13 @@
         </is>
       </c>
       <c r="L189" s="3" t="n">
-        <v>5.26</v>
+        <v>2.3</v>
       </c>
       <c r="M189" s="3" t="n">
-        <v>40.74</v>
+        <v>44.36</v>
       </c>
       <c r="N189" s="3" t="n">
-        <v>-7.8498</v>
+        <v>-13.3787</v>
       </c>
       <c r="O189" s="3" t="n">
         <v>0</v>
@@ -12777,28 +12777,28 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>OIBR3</t>
+          <t>CSAN3</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>Não Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="C190" s="3" t="n">
-        <v>27.4</v>
+        <v>62.9</v>
       </c>
       <c r="D190" s="3" t="n">
-        <v>0.19</v>
+        <v>6.29</v>
       </c>
       <c r="E190" s="3" t="n">
-        <v>0.12</v>
+        <v>3.8</v>
       </c>
       <c r="F190" s="3" t="n">
-        <v>-36.84</v>
+        <v>-39.59</v>
       </c>
       <c r="G190" s="3" t="n">
-        <v>-364.44</v>
+        <v>-3.36</v>
       </c>
       <c r="H190" s="3" t="inlineStr">
         <is>
@@ -12821,13 +12821,13 @@
         </is>
       </c>
       <c r="L190" s="3" t="n">
-        <v>0.2</v>
+        <v>0.58</v>
       </c>
       <c r="M190" s="3" t="n">
-        <v>139.02</v>
+        <v>12.23</v>
       </c>
       <c r="N190" s="3" t="n">
-        <v>-89.8707</v>
+        <v>-0.7196</v>
       </c>
       <c r="O190" s="3" t="n">
         <v>0</v>
@@ -12842,7 +12842,7 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>ARML3</t>
+          <t>PCAR3</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -12851,19 +12851,19 @@
         </is>
       </c>
       <c r="C191" s="3" t="n">
-        <v>40.3</v>
+        <v>35.5</v>
       </c>
       <c r="D191" s="3" t="n">
-        <v>5.9</v>
+        <v>3.08</v>
       </c>
       <c r="E191" s="3" t="n">
-        <v>3.65</v>
+        <v>1.86</v>
       </c>
       <c r="F191" s="3" t="n">
-        <v>-38.14</v>
+        <v>-39.61</v>
       </c>
       <c r="G191" s="3" t="n">
-        <v>17.68</v>
+        <v>1.51</v>
       </c>
       <c r="H191" s="3" t="inlineStr">
         <is>
@@ -12886,13 +12886,13 @@
         </is>
       </c>
       <c r="L191" s="3" t="n">
-        <v>0.76</v>
+        <v>1.47</v>
       </c>
       <c r="M191" s="3" t="n">
-        <v>18.97</v>
+        <v>64.61</v>
       </c>
       <c r="N191" s="3" t="n">
-        <v>-1.038</v>
+        <v>-26.7482</v>
       </c>
       <c r="O191" s="3" t="n">
         <v>0</v>
@@ -12907,32 +12907,32 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>PGMN3</t>
+          <t>PTBL3</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>Não Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="C192" s="3" t="n">
-        <v>38.7</v>
+        <v>61.3</v>
       </c>
       <c r="D192" s="3" t="n">
-        <v>6.97</v>
+        <v>3.22</v>
       </c>
       <c r="E192" s="3" t="n">
-        <v>4.27</v>
+        <v>1.88</v>
       </c>
       <c r="F192" s="3" t="n">
-        <v>-38.74</v>
+        <v>-41.61</v>
       </c>
       <c r="G192" s="3" t="n">
-        <v>26.56</v>
+        <v>-11.96</v>
       </c>
       <c r="H192" s="3" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="I192" s="3" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="K192" s="3" t="inlineStr">
@@ -12951,13 +12951,13 @@
         </is>
       </c>
       <c r="L192" s="3" t="n">
-        <v>2.3</v>
+        <v>0.48</v>
       </c>
       <c r="M192" s="3" t="n">
-        <v>44.36</v>
+        <v>22.29</v>
       </c>
       <c r="N192" s="3" t="n">
-        <v>-13.3787</v>
+        <v>-0.3967</v>
       </c>
       <c r="O192" s="3" t="n">
         <v>0</v>
@@ -12972,32 +12972,32 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>CSAN3</t>
+          <t>PLPL3</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Não Previsível</t>
         </is>
       </c>
       <c r="C193" s="3" t="n">
-        <v>62.9</v>
+        <v>38.7</v>
       </c>
       <c r="D193" s="3" t="n">
-        <v>6.29</v>
+        <v>15.47</v>
       </c>
       <c r="E193" s="3" t="n">
-        <v>3.8</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="F193" s="3" t="n">
-        <v>-39.59</v>
+        <v>-42.66</v>
       </c>
       <c r="G193" s="3" t="n">
-        <v>-3.36</v>
+        <v>3.95</v>
       </c>
       <c r="H193" s="3" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="I193" s="3" t="inlineStr">
@@ -13007,7 +13007,7 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="K193" s="3" t="inlineStr">
@@ -13016,13 +13016,13 @@
         </is>
       </c>
       <c r="L193" s="3" t="n">
-        <v>0.58</v>
+        <v>3.23</v>
       </c>
       <c r="M193" s="3" t="n">
-        <v>12.23</v>
+        <v>29.62</v>
       </c>
       <c r="N193" s="3" t="n">
-        <v>-0.7196</v>
+        <v>-3.1941</v>
       </c>
       <c r="O193" s="3" t="n">
         <v>0</v>
@@ -13037,7 +13037,7 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>PCAR3</t>
+          <t>RAIZ4</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -13046,23 +13046,23 @@
         </is>
       </c>
       <c r="C194" s="3" t="n">
-        <v>35.5</v>
+        <v>50</v>
       </c>
       <c r="D194" s="3" t="n">
-        <v>3.08</v>
+        <v>0.63</v>
       </c>
       <c r="E194" s="3" t="n">
-        <v>1.86</v>
+        <v>0.36</v>
       </c>
       <c r="F194" s="3" t="n">
-        <v>-39.61</v>
+        <v>-42.86</v>
       </c>
       <c r="G194" s="3" t="n">
-        <v>1.51</v>
+        <v>-35.84</v>
       </c>
       <c r="H194" s="3" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="I194" s="3" t="inlineStr">
@@ -13072,7 +13072,7 @@
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="K194" s="3" t="inlineStr">
@@ -13081,13 +13081,13 @@
         </is>
       </c>
       <c r="L194" s="3" t="n">
-        <v>1.47</v>
+        <v>0.05</v>
       </c>
       <c r="M194" s="3" t="n">
-        <v>64.61</v>
+        <v>10.93</v>
       </c>
       <c r="N194" s="3" t="n">
-        <v>-26.7482</v>
+        <v>0.0804</v>
       </c>
       <c r="O194" s="3" t="n">
         <v>0</v>
@@ -13102,32 +13102,32 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>PTBL3</t>
+          <t>MRVE3</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Não Previsível</t>
         </is>
       </c>
       <c r="C195" s="3" t="n">
-        <v>61.3</v>
+        <v>32.3</v>
       </c>
       <c r="D195" s="3" t="n">
-        <v>3.22</v>
+        <v>10.24</v>
       </c>
       <c r="E195" s="3" t="n">
-        <v>1.88</v>
+        <v>5.85</v>
       </c>
       <c r="F195" s="3" t="n">
-        <v>-41.61</v>
+        <v>-42.87</v>
       </c>
       <c r="G195" s="3" t="n">
-        <v>-11.96</v>
+        <v>11.58</v>
       </c>
       <c r="H195" s="3" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="I195" s="3" t="inlineStr">
@@ -13137,7 +13137,7 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="K195" s="3" t="inlineStr">
@@ -13146,13 +13146,13 @@
         </is>
       </c>
       <c r="L195" s="3" t="n">
-        <v>0.48</v>
+        <v>2.23</v>
       </c>
       <c r="M195" s="3" t="n">
-        <v>22.29</v>
+        <v>32.47</v>
       </c>
       <c r="N195" s="3" t="n">
-        <v>-0.3967</v>
+        <v>-4.8477</v>
       </c>
       <c r="O195" s="3" t="n">
         <v>0</v>
@@ -13167,32 +13167,32 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>PLPL3</t>
+          <t>LIGT3</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>Não Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="C196" s="3" t="n">
-        <v>38.7</v>
+        <v>54.8</v>
       </c>
       <c r="D196" s="3" t="n">
-        <v>15.47</v>
+        <v>4.93</v>
       </c>
       <c r="E196" s="3" t="n">
-        <v>8.869999999999999</v>
+        <v>2.73</v>
       </c>
       <c r="F196" s="3" t="n">
-        <v>-42.66</v>
+        <v>-44.62</v>
       </c>
       <c r="G196" s="3" t="n">
-        <v>3.95</v>
+        <v>-14.89</v>
       </c>
       <c r="H196" s="3" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="I196" s="3" t="inlineStr">
@@ -13202,7 +13202,7 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="K196" s="3" t="inlineStr">
@@ -13211,13 +13211,13 @@
         </is>
       </c>
       <c r="L196" s="3" t="n">
-        <v>3.23</v>
+        <v>0.65</v>
       </c>
       <c r="M196" s="3" t="n">
-        <v>29.62</v>
+        <v>15.22</v>
       </c>
       <c r="N196" s="3" t="n">
-        <v>-3.1941</v>
+        <v>0.0495</v>
       </c>
       <c r="O196" s="3" t="n">
         <v>0</v>
@@ -13232,7 +13232,7 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>RAIZ4</t>
+          <t>PMAM3</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -13244,16 +13244,16 @@
         <v>50</v>
       </c>
       <c r="D197" s="3" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="E197" s="3" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="F197" s="3" t="n">
-        <v>-42.86</v>
+        <v>-48.44</v>
       </c>
       <c r="G197" s="3" t="n">
-        <v>-35.84</v>
+        <v>-93.36</v>
       </c>
       <c r="H197" s="3" t="inlineStr">
         <is>
@@ -13276,13 +13276,13 @@
         </is>
       </c>
       <c r="L197" s="3" t="n">
-        <v>0.05</v>
+        <v>0.26</v>
       </c>
       <c r="M197" s="3" t="n">
-        <v>10.93</v>
+        <v>50.61</v>
       </c>
       <c r="N197" s="3" t="n">
-        <v>0.0804</v>
+        <v>-19.6847</v>
       </c>
       <c r="O197" s="3" t="n">
         <v>0</v>
@@ -13297,32 +13297,32 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>MRVE3</t>
+          <t>ONCO3</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>Não Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="C198" s="3" t="n">
-        <v>32.3</v>
+        <v>58.1</v>
       </c>
       <c r="D198" s="3" t="n">
-        <v>10.24</v>
+        <v>2.65</v>
       </c>
       <c r="E198" s="3" t="n">
-        <v>5.85</v>
+        <v>1.34</v>
       </c>
       <c r="F198" s="3" t="n">
-        <v>-42.87</v>
+        <v>-49.43</v>
       </c>
       <c r="G198" s="3" t="n">
-        <v>11.58</v>
+        <v>-53.22</v>
       </c>
       <c r="H198" s="3" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="I198" s="3" t="inlineStr">
@@ -13332,7 +13332,7 @@
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="K198" s="3" t="inlineStr">
@@ -13341,13 +13341,13 @@
         </is>
       </c>
       <c r="L198" s="3" t="n">
-        <v>2.23</v>
+        <v>0.35</v>
       </c>
       <c r="M198" s="3" t="n">
-        <v>32.47</v>
+        <v>20.5</v>
       </c>
       <c r="N198" s="3" t="n">
-        <v>-4.8477</v>
+        <v>-0.2804</v>
       </c>
       <c r="O198" s="3" t="n">
         <v>0</v>
@@ -13362,28 +13362,28 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>LIGT3</t>
+          <t>GFSA3</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="C199" s="3" t="n">
-        <v>54.8</v>
+        <v>59.7</v>
       </c>
       <c r="D199" s="3" t="n">
-        <v>4.93</v>
+        <v>2.37</v>
       </c>
       <c r="E199" s="3" t="n">
-        <v>2.73</v>
+        <v>1.13</v>
       </c>
       <c r="F199" s="3" t="n">
-        <v>-44.62</v>
+        <v>-52.32</v>
       </c>
       <c r="G199" s="3" t="n">
-        <v>-14.89</v>
+        <v>-491.29</v>
       </c>
       <c r="H199" s="3" t="inlineStr">
         <is>
@@ -13406,13 +13406,13 @@
         </is>
       </c>
       <c r="L199" s="3" t="n">
-        <v>0.65</v>
+        <v>3.19</v>
       </c>
       <c r="M199" s="3" t="n">
-        <v>15.22</v>
+        <v>228.76</v>
       </c>
       <c r="N199" s="3" t="n">
-        <v>0.0495</v>
+        <v>-128.6804</v>
       </c>
       <c r="O199" s="3" t="n">
         <v>0</v>
@@ -13427,28 +13427,28 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>PMAM3</t>
+          <t>BHIA3</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>Não Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="C200" s="3" t="n">
-        <v>50</v>
+        <v>59.7</v>
       </c>
       <c r="D200" s="3" t="n">
-        <v>0.64</v>
+        <v>2.99</v>
       </c>
       <c r="E200" s="3" t="n">
-        <v>0.33</v>
+        <v>1.36</v>
       </c>
       <c r="F200" s="3" t="n">
-        <v>-48.44</v>
+        <v>-54.52</v>
       </c>
       <c r="G200" s="3" t="n">
-        <v>-93.36</v>
+        <v>-9.69</v>
       </c>
       <c r="H200" s="3" t="inlineStr">
         <is>
@@ -13471,13 +13471,13 @@
         </is>
       </c>
       <c r="L200" s="3" t="n">
-        <v>0.26</v>
+        <v>0.4</v>
       </c>
       <c r="M200" s="3" t="n">
-        <v>50.61</v>
+        <v>23.2</v>
       </c>
       <c r="N200" s="3" t="n">
-        <v>-19.6847</v>
+        <v>-0.2302</v>
       </c>
       <c r="O200" s="3" t="n">
         <v>0</v>
@@ -13492,28 +13492,28 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>ONCO3</t>
+          <t>SEQL3</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Não Previsível</t>
         </is>
       </c>
       <c r="C201" s="3" t="n">
-        <v>58.1</v>
+        <v>45.2</v>
       </c>
       <c r="D201" s="3" t="n">
-        <v>2.65</v>
+        <v>0.32</v>
       </c>
       <c r="E201" s="3" t="n">
-        <v>1.34</v>
+        <v>0.12</v>
       </c>
       <c r="F201" s="3" t="n">
-        <v>-49.43</v>
+        <v>-62.5</v>
       </c>
       <c r="G201" s="3" t="n">
-        <v>-53.22</v>
+        <v>-1869.1</v>
       </c>
       <c r="H201" s="3" t="inlineStr">
         <is>
@@ -13536,13 +13536,13 @@
         </is>
       </c>
       <c r="L201" s="3" t="n">
-        <v>0.35</v>
+        <v>2.54</v>
       </c>
       <c r="M201" s="3" t="n">
-        <v>20.5</v>
+        <v>1822.28</v>
       </c>
       <c r="N201" s="3" t="n">
-        <v>-0.2804</v>
+        <v>-1536.0128</v>
       </c>
       <c r="O201" s="3" t="n">
         <v>0</v>
@@ -13557,32 +13557,32 @@
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>GFSA3</t>
+          <t>RCSL4</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Não Previsível</t>
         </is>
       </c>
       <c r="C202" s="3" t="n">
-        <v>59.7</v>
+        <v>32.3</v>
       </c>
       <c r="D202" s="3" t="n">
-        <v>2.37</v>
+        <v>1.46</v>
       </c>
       <c r="E202" s="3" t="n">
-        <v>1.13</v>
+        <v>0.53</v>
       </c>
       <c r="F202" s="3" t="n">
-        <v>-52.32</v>
+        <v>-63.76</v>
       </c>
       <c r="G202" s="3" t="n">
-        <v>-491.29</v>
+        <v>46.33</v>
       </c>
       <c r="H202" s="3" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="I202" s="3" t="inlineStr">
@@ -13592,7 +13592,7 @@
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="K202" s="3" t="inlineStr">
@@ -13601,13 +13601,13 @@
         </is>
       </c>
       <c r="L202" s="3" t="n">
-        <v>3.19</v>
+        <v>1.63</v>
       </c>
       <c r="M202" s="3" t="n">
-        <v>228.76</v>
+        <v>248.39</v>
       </c>
       <c r="N202" s="3" t="n">
-        <v>-128.6804</v>
+        <v>-28.7057</v>
       </c>
       <c r="O202" s="3" t="n">
         <v>0</v>
@@ -13616,201 +13616,6 @@
         <v>0</v>
       </c>
       <c r="Q202" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="3" t="inlineStr">
-        <is>
-          <t>BHIA3</t>
-        </is>
-      </c>
-      <c r="B203" s="3" t="inlineStr">
-        <is>
-          <t>Muito Previsível</t>
-        </is>
-      </c>
-      <c r="C203" s="3" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="D203" s="3" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="E203" s="3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="F203" s="3" t="n">
-        <v>-54.52</v>
-      </c>
-      <c r="G203" s="3" t="n">
-        <v>-9.69</v>
-      </c>
-      <c r="H203" s="3" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="I203" s="3" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="J203" s="3" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="K203" s="3" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="L203" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M203" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="N203" s="3" t="n">
-        <v>-0.2302</v>
-      </c>
-      <c r="O203" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P203" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q203" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="3" t="inlineStr">
-        <is>
-          <t>SEQL3</t>
-        </is>
-      </c>
-      <c r="B204" s="3" t="inlineStr">
-        <is>
-          <t>Não Previsível</t>
-        </is>
-      </c>
-      <c r="C204" s="3" t="n">
-        <v>45.2</v>
-      </c>
-      <c r="D204" s="3" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E204" s="3" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="F204" s="3" t="n">
-        <v>-62.5</v>
-      </c>
-      <c r="G204" s="3" t="n">
-        <v>-1869.1</v>
-      </c>
-      <c r="H204" s="3" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="I204" s="3" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="J204" s="3" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="K204" s="3" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="L204" s="3" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="M204" s="3" t="n">
-        <v>1822.28</v>
-      </c>
-      <c r="N204" s="3" t="n">
-        <v>-1536.0128</v>
-      </c>
-      <c r="O204" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P204" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q204" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="3" t="inlineStr">
-        <is>
-          <t>RCSL4</t>
-        </is>
-      </c>
-      <c r="B205" s="3" t="inlineStr">
-        <is>
-          <t>Não Previsível</t>
-        </is>
-      </c>
-      <c r="C205" s="3" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="D205" s="3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="E205" s="3" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="F205" s="3" t="n">
-        <v>-63.76</v>
-      </c>
-      <c r="G205" s="3" t="n">
-        <v>46.33</v>
-      </c>
-      <c r="H205" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="I205" s="3" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="J205" s="3" t="inlineStr">
-        <is>
-          <t>❌ NÃO</t>
-        </is>
-      </c>
-      <c r="K205" s="3" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="L205" s="3" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="M205" s="3" t="n">
-        <v>248.39</v>
-      </c>
-      <c r="N205" s="3" t="n">
-        <v>-28.7057</v>
-      </c>
-      <c r="O205" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P205" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q205" s="3" t="n">
         <v>0</v>
       </c>
     </row>
